--- a/STAIX2026/assets/Poster-Presentation-Label-Assignment.xlsx
+++ b/STAIX2026/assets/Poster-Presentation-Label-Assignment.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tracyke/Dropbox/Mac (2)/Documents/2026/STAI-X conference/Poster session/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A941688F-34DC-354B-A1ED-A1507CB729C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B21276E5-A52B-1040-B89A-1D24086F1E8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9000" yWindow="4080" windowWidth="38400" windowHeight="19240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Assignment" sheetId="7" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="149">
   <si>
     <t>Design-Based Supervised Learning with Noisy Human Labels</t>
   </si>
@@ -98,9 +98,6 @@
     <t>Grading the Grader: Lessons from Evaluating an Agentic Data Analysis System</t>
   </si>
   <si>
-    <t>AI-Augmented Statistical Network Estimation with Proxy Gene Embeddings</t>
-  </si>
-  <si>
     <t>Adaptive Kernel Density Estimation with Pre-training</t>
   </si>
   <si>
@@ -143,9 +140,6 @@
     <t>Bridging Probabilistic LLMs and Deterministic Statistical Validation: The PROVE Multi-Agent Framework for Clinical Trial Reporting</t>
   </si>
   <si>
-    <t>Honorable</t>
-  </si>
-  <si>
     <t>Transformers as Provable Approximators of Sparse Principal Component Analysis</t>
   </si>
   <si>
@@ -158,9 +152,6 @@
     <t>STAVAT: Stratified Anytime-Valid Atom Sampling for LLM Tier Placement</t>
   </si>
   <si>
-    <t>Optimal Self-Distillation for Rectified Flow via Linear Probing</t>
-  </si>
-  <si>
     <t>VADR: Variance Adjusted Distribution Regression</t>
   </si>
   <si>
@@ -461,20 +452,41 @@
     <t>Poster (extended abstract track)</t>
   </si>
   <si>
-    <t>81-88</t>
-  </si>
-  <si>
-    <t>132-134</t>
-  </si>
-  <si>
     <t>Paper Honorable</t>
+  </si>
+  <si>
+    <t>prediction-only distillation with optimal mixing in ridge-regularized linear and logistic regression</t>
+  </si>
+  <si>
+    <t>Vertical Consensus Inference for High-Dimensional Random Partition</t>
+  </si>
+  <si>
+    <t>Sliced-Regularized Optimal Transport</t>
+  </si>
+  <si>
+    <t>Neural $\xi$: Learning the Radon--Nikodym Derivative for Option Pricing</t>
+  </si>
+  <si>
+    <t>StatEval: A Comprehensive Benchmark for Large Language Models in Statistics</t>
+  </si>
+  <si>
+    <t>A HIPAA-Safe Multi-Agent LLM Workflow for Data Science Research on CMS Medicaid Claims</t>
+  </si>
+  <si>
+    <t>When Majority Vote Fails: Pseudo-Gold Standards in AI Diagnostic Evaluation</t>
+  </si>
+  <si>
+    <t>Precision Physical Activity Prescription via Reinforcement Learning for Functional Actions</t>
+  </si>
+  <si>
+    <t>86-88</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -514,6 +526,13 @@
       <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="2" tint="-0.14999847407452621"/>
       <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -581,14 +600,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -617,6 +635,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -866,13 +891,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>12700</xdr:colOff>
-      <xdr:row>131</xdr:row>
+      <xdr:row>138</xdr:row>
       <xdr:rowOff>12700</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>266699</xdr:colOff>
-      <xdr:row>175</xdr:row>
+      <xdr:row>182</xdr:row>
       <xdr:rowOff>113505</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1106,31 +1131,31 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D22663D-DF04-F34F-B5CE-C0BD0EE02426}">
-  <dimension ref="A1:I130"/>
+  <dimension ref="A1:I137"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10.6640625" customWidth="1"/>
     <col min="2" max="2" width="99" customWidth="1"/>
     <col min="3" max="3" width="13.6640625" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" style="9"/>
+    <col min="4" max="4" width="10.83203125" style="8"/>
     <col min="5" max="5" width="23.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="4" customFormat="1" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="D1" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="E1" s="11" t="s">
         <v>130</v>
-      </c>
-      <c r="C1" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="E1" s="12" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
@@ -1140,14 +1165,14 @@
       <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="9">
+      <c r="D2" s="8">
         <v>1</v>
       </c>
       <c r="E2" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="15" t="s">
-        <v>134</v>
+      <c r="I2" s="14" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.15">
@@ -1157,680 +1182,681 @@
       <c r="B3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="9">
+      <c r="D3" s="8">
         <v>2</v>
       </c>
       <c r="E3" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="16"/>
+      <c r="I3" s="15"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A4" s="1">
         <v>84</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C4" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="9">
+      <c r="D4" s="8">
         <v>3</v>
       </c>
       <c r="E4" t="s">
         <v>4</v>
       </c>
-      <c r="I4" s="16"/>
+      <c r="I4" s="15"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A5" s="2">
         <v>22</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D5" s="9">
+        <v>48</v>
+      </c>
+      <c r="D5" s="8">
         <v>4</v>
       </c>
       <c r="E5" t="s">
         <v>4</v>
       </c>
-      <c r="I5" s="16"/>
+      <c r="I5" s="15"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A6" s="2">
         <v>28</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D6" s="9">
+        <v>50</v>
+      </c>
+      <c r="D6" s="8">
         <v>5</v>
       </c>
       <c r="E6" t="s">
         <v>4</v>
       </c>
-      <c r="I6" s="16"/>
+      <c r="I6" s="15"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A7" s="3">
         <v>11</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="D7" s="9">
+        <v>72</v>
+      </c>
+      <c r="D7" s="8">
         <v>6</v>
       </c>
       <c r="E7" t="s">
         <v>4</v>
       </c>
-      <c r="I7" s="16"/>
+      <c r="I7" s="15"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A8" s="3">
         <v>15</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="D8" s="9">
+        <v>74</v>
+      </c>
+      <c r="D8" s="8">
         <v>7</v>
       </c>
       <c r="E8" t="s">
         <v>4</v>
       </c>
-      <c r="I8" s="16"/>
+      <c r="I8" s="15"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A9" s="3">
         <v>39</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="D9" s="9">
+        <v>90</v>
+      </c>
+      <c r="D9" s="8">
         <v>8</v>
       </c>
       <c r="E9" t="s">
         <v>4</v>
       </c>
-      <c r="I9" s="16"/>
+      <c r="I9" s="15"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A10" s="3">
         <v>58</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="D10" s="9">
+        <v>103</v>
+      </c>
+      <c r="D10" s="8">
         <v>9</v>
       </c>
       <c r="E10" t="s">
         <v>4</v>
       </c>
-      <c r="I10" s="16"/>
+      <c r="I10" s="15"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A11" s="1">
         <v>119</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D11" s="9">
+        <v>37</v>
+      </c>
+      <c r="D11" s="8">
         <v>10</v>
       </c>
       <c r="E11" t="s">
         <v>4</v>
       </c>
-      <c r="I11" s="16"/>
+      <c r="I11" s="15"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A12" s="1">
         <v>130</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C12" t="s">
-        <v>36</v>
-      </c>
-      <c r="D12" s="9">
+        <v>42</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="D12" s="8">
         <v>11</v>
       </c>
       <c r="E12" t="s">
         <v>4</v>
       </c>
-      <c r="I12" s="16"/>
+      <c r="I12" s="15"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A13" s="2">
-        <v>136</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D13" s="9">
+      <c r="A13" s="3">
+        <v>63</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D13" s="8">
         <v>12</v>
       </c>
       <c r="E13" t="s">
         <v>4</v>
       </c>
-      <c r="I13" s="16"/>
+      <c r="I13" s="15"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A14" s="3">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="D14" s="9">
+        <v>107</v>
+      </c>
+      <c r="D14" s="8">
         <v>13</v>
       </c>
       <c r="E14" t="s">
         <v>4</v>
       </c>
-      <c r="I14" s="16"/>
+      <c r="I14" s="15"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A15" s="3">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="D15" s="9">
+        <v>112</v>
+      </c>
+      <c r="D15" s="8">
         <v>14</v>
       </c>
       <c r="E15" t="s">
         <v>4</v>
       </c>
-      <c r="I15" s="16"/>
+      <c r="I15" s="15"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A16" s="3">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="D16" s="9">
+        <v>114</v>
+      </c>
+      <c r="D16" s="8">
         <v>15</v>
       </c>
       <c r="E16" t="s">
         <v>4</v>
       </c>
-      <c r="I16" s="16"/>
+      <c r="I16" s="15"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A17" s="3">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="D17" s="9">
+        <v>116</v>
+      </c>
+      <c r="D17" s="8">
         <v>16</v>
       </c>
       <c r="E17" t="s">
         <v>4</v>
       </c>
-      <c r="I17" s="16"/>
+      <c r="I17" s="15"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A18" s="3">
-        <v>75</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="D18" s="9">
+      <c r="A18" s="1">
+        <v>29</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D18" s="8">
         <v>17</v>
       </c>
       <c r="E18" t="s">
-        <v>4</v>
-      </c>
-      <c r="I18" s="16"/>
+        <v>8</v>
+      </c>
+      <c r="I18" s="15"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A19" s="1">
-        <v>29</v>
+        <v>78</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D19" s="9">
+        <v>24</v>
+      </c>
+      <c r="D19" s="8">
         <v>18</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
       </c>
-      <c r="I19" s="16"/>
+      <c r="I19" s="15"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A20" s="1">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D20" s="9">
+        <v>29</v>
+      </c>
+      <c r="D20" s="8">
         <v>19</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
       </c>
-      <c r="I20" s="16"/>
+      <c r="I20" s="15"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A21" s="1">
-        <v>91</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D21" s="9">
+      <c r="A21" s="2">
+        <v>35</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D21" s="8">
         <v>20</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
       </c>
-      <c r="I21" s="16"/>
+      <c r="I21" s="15"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A22" s="2">
-        <v>35</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D22" s="9">
+      <c r="A22" s="3">
+        <v>1</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D22" s="8">
         <v>21</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
       </c>
-      <c r="I22" s="16"/>
+      <c r="I22" s="15"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A23" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D23" s="9">
+        <v>66</v>
+      </c>
+      <c r="D23" s="8">
         <v>22</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
       </c>
-      <c r="I23" s="16"/>
+      <c r="I23" s="15"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A24" s="3">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D24" s="9">
+        <v>77</v>
+      </c>
+      <c r="D24" s="8">
         <v>23</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
       </c>
-      <c r="I24" s="16"/>
+      <c r="I24" s="15"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A25" s="3">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D25" s="9">
+        <v>86</v>
+      </c>
+      <c r="C25" t="s">
+        <v>68</v>
+      </c>
+      <c r="D25" s="8">
         <v>24</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
       </c>
-      <c r="I25" s="16"/>
+      <c r="I25" s="15"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A26" s="3">
-        <v>35</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="C26" t="s">
-        <v>71</v>
-      </c>
-      <c r="D26" s="9">
+      <c r="A26" s="2">
+        <v>106</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D26" s="8">
         <v>25</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
       </c>
-      <c r="I26" s="16"/>
+      <c r="I26" s="15"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A27" s="2">
-        <v>106</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D27" s="9">
+      <c r="A27" s="1">
+        <v>101</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C27" t="s">
+        <v>13</v>
+      </c>
+      <c r="D27" s="8">
         <v>26</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
       </c>
-      <c r="I27" s="16"/>
+      <c r="I27" s="15"/>
     </row>
     <row r="28" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="1">
-        <v>101</v>
+        <v>129</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C28" t="s">
-        <v>13</v>
-      </c>
-      <c r="D28" s="9">
+        <v>41</v>
+      </c>
+      <c r="D28" s="8">
         <v>27</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
       </c>
-      <c r="I28" s="16"/>
+      <c r="I28" s="15"/>
     </row>
     <row r="29" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="1">
-        <v>123</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D29" s="9">
+      <c r="A29" s="3">
+        <v>38</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C29" t="s">
+        <v>68</v>
+      </c>
+      <c r="D29" s="8">
         <v>28</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
       </c>
-      <c r="I29" s="16"/>
+      <c r="I29" s="15"/>
     </row>
     <row r="30" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="1">
-        <v>129</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D30" s="9">
+      <c r="A30" s="3">
+        <v>67</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D30" s="8">
         <v>29</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
       </c>
-      <c r="I30" s="16"/>
+      <c r="I30" s="15"/>
     </row>
     <row r="31" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="3">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="C31" t="s">
-        <v>71</v>
-      </c>
-      <c r="D31" s="9">
+        <v>117</v>
+      </c>
+      <c r="D31" s="8">
         <v>30</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
       </c>
-      <c r="I31" s="16"/>
+      <c r="I31" s="15"/>
     </row>
     <row r="32" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="3">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="D32" s="9">
+        <v>118</v>
+      </c>
+      <c r="D32" s="8">
         <v>31</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
       </c>
-      <c r="I32" s="16"/>
+      <c r="I32" s="15"/>
     </row>
     <row r="33" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="3">
-        <v>77</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="D33" s="9">
+      <c r="A33" s="2">
+        <v>129</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D33" s="8">
         <v>32</v>
       </c>
       <c r="E33" t="s">
         <v>8</v>
       </c>
-      <c r="I33" s="16"/>
+      <c r="I33" s="15"/>
     </row>
     <row r="34" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="3">
-        <v>78</v>
+        <v>22</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="D34" s="9">
+        <v>146</v>
+      </c>
+      <c r="D34" s="8">
         <v>33</v>
       </c>
       <c r="E34" t="s">
-        <v>8</v>
-      </c>
-      <c r="I34" s="16"/>
+        <v>14</v>
+      </c>
+      <c r="I34" s="15"/>
     </row>
     <row r="35" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A35" s="2">
-        <v>129</v>
-      </c>
-      <c r="B35" s="2" t="s">
+      <c r="A35" s="1">
         <v>44</v>
       </c>
-      <c r="D35" s="9">
+      <c r="B35" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C35" t="s">
+        <v>13</v>
+      </c>
+      <c r="D35" s="8">
         <v>34</v>
       </c>
       <c r="E35" t="s">
-        <v>8</v>
-      </c>
-      <c r="I35" s="16"/>
+        <v>14</v>
+      </c>
+      <c r="I35" s="15"/>
     </row>
     <row r="36" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="1">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C36" t="s">
-        <v>13</v>
-      </c>
-      <c r="D36" s="9">
+        <v>15</v>
+      </c>
+      <c r="D36" s="8">
         <v>35</v>
       </c>
       <c r="E36" t="s">
         <v>14</v>
       </c>
-      <c r="I36" s="16"/>
+      <c r="I36" s="15"/>
     </row>
     <row r="37" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="1">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D37" s="9">
+        <v>16</v>
+      </c>
+      <c r="D37" s="8">
         <v>36</v>
       </c>
       <c r="E37" t="s">
         <v>14</v>
       </c>
-      <c r="I37" s="16"/>
+      <c r="I37" s="15"/>
     </row>
     <row r="38" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A38" s="1">
+      <c r="A38" s="2">
+        <v>26</v>
+      </c>
+      <c r="B38" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B38" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D38" s="9">
+      <c r="D38" s="8">
         <v>37</v>
       </c>
       <c r="E38" t="s">
         <v>14</v>
       </c>
-      <c r="I38" s="16"/>
+      <c r="I38" s="15"/>
     </row>
     <row r="39" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="2">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D39" s="9">
+      <c r="D39" s="8">
         <v>38</v>
       </c>
       <c r="E39" t="s">
         <v>14</v>
       </c>
-      <c r="I39" s="16"/>
+      <c r="I39" s="15"/>
     </row>
     <row r="40" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A40" s="2">
-        <v>46</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D40" s="9">
+      <c r="A40" s="3">
+        <v>3</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C40" t="s">
+        <v>68</v>
+      </c>
+      <c r="D40" s="8">
         <v>39</v>
       </c>
       <c r="E40" t="s">
         <v>14</v>
       </c>
-      <c r="I40" s="16"/>
+      <c r="I40" s="15"/>
     </row>
     <row r="41" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="3">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C41" t="s">
         <v>71</v>
       </c>
-      <c r="D41" s="9">
+      <c r="D41" s="8">
         <v>40</v>
       </c>
       <c r="E41" t="s">
         <v>14</v>
       </c>
-      <c r="I41" s="16"/>
+      <c r="I41" s="15"/>
     </row>
     <row r="42" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="3">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D42" s="9">
+        <v>73</v>
+      </c>
+      <c r="D42" s="8">
         <v>41</v>
       </c>
       <c r="E42" t="s">
         <v>14</v>
       </c>
-      <c r="I42" s="16"/>
+      <c r="I42" s="15"/>
     </row>
     <row r="43" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="3">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="D43" s="9">
+        <v>85</v>
+      </c>
+      <c r="D43" s="8">
         <v>42</v>
       </c>
       <c r="E43" t="s">
         <v>14</v>
       </c>
-      <c r="I43" s="16"/>
+      <c r="I43" s="15"/>
     </row>
     <row r="44" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A44" s="3">
-        <v>32</v>
-      </c>
-      <c r="B44" s="3" t="s">
+      <c r="A44" s="23">
+        <v>37</v>
+      </c>
+      <c r="B44" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="D44" s="9">
+      <c r="C44" s="24"/>
+      <c r="D44" s="8">
         <v>43</v>
       </c>
-      <c r="E44" t="s">
-        <v>14</v>
-      </c>
-      <c r="I44" s="16"/>
+      <c r="E44" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="F44" s="24"/>
+      <c r="G44" s="24"/>
+      <c r="I44" s="15"/>
     </row>
     <row r="45" spans="1:9" s="4" customFormat="1" ht="13" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="6">
-        <v>37</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="D45" s="8">
+      <c r="A45" s="25"/>
+      <c r="B45" s="25"/>
+      <c r="C45" s="25"/>
+      <c r="D45" s="26">
         <v>44</v>
       </c>
-      <c r="E45" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I45" s="17"/>
+      <c r="E45" s="25"/>
+      <c r="F45" s="25"/>
+      <c r="G45" s="25"/>
+      <c r="H45" s="25"/>
+      <c r="I45" s="16"/>
     </row>
     <row r="46" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="3">
         <v>40</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="D46" s="9">
+        <v>91</v>
+      </c>
+      <c r="D46" s="8">
         <v>45</v>
       </c>
       <c r="E46" t="s">
         <v>14</v>
       </c>
-      <c r="I46" s="18" t="s">
-        <v>135</v>
+      <c r="I46" s="17" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
@@ -1838,15 +1864,15 @@
         <v>45</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="D47" s="9">
+        <v>94</v>
+      </c>
+      <c r="D47" s="8">
         <v>46</v>
       </c>
       <c r="E47" t="s">
         <v>14</v>
       </c>
-      <c r="I47" s="19"/>
+      <c r="I47" s="18"/>
     </row>
     <row r="48" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="1">
@@ -1855,1251 +1881,1362 @@
       <c r="B48" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D48" s="9">
+      <c r="D48" s="8">
         <v>47</v>
       </c>
       <c r="E48" t="s">
         <v>14</v>
       </c>
-      <c r="I48" s="19"/>
+      <c r="I48" s="18"/>
     </row>
     <row r="49" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="1">
         <v>63</v>
       </c>
-      <c r="B49" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D49" s="9">
+      <c r="B49" s="20" t="s">
+        <v>140</v>
+      </c>
+      <c r="D49" s="8">
         <v>48</v>
       </c>
       <c r="E49" t="s">
         <v>14</v>
       </c>
-      <c r="I49" s="19"/>
+      <c r="I49" s="18"/>
     </row>
     <row r="50" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="1">
         <v>93</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D50" s="9">
+        <v>30</v>
+      </c>
+      <c r="D50" s="8">
         <v>49</v>
       </c>
       <c r="E50" t="s">
         <v>14</v>
       </c>
-      <c r="I50" s="19"/>
+      <c r="I50" s="18"/>
     </row>
     <row r="51" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="1">
         <v>107</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D51" s="9">
+        <v>33</v>
+      </c>
+      <c r="D51" s="8">
         <v>50</v>
       </c>
       <c r="E51" t="s">
         <v>14</v>
       </c>
-      <c r="I51" s="19"/>
+      <c r="I51" s="18"/>
     </row>
     <row r="52" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="2">
         <v>75</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D52" s="9">
+        <v>57</v>
+      </c>
+      <c r="D52" s="8">
         <v>51</v>
       </c>
       <c r="E52" t="s">
         <v>14</v>
       </c>
-      <c r="I52" s="19"/>
+      <c r="I52" s="18"/>
     </row>
     <row r="53" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="2">
         <v>96</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D53" s="9">
+        <v>58</v>
+      </c>
+      <c r="D53" s="8">
         <v>52</v>
       </c>
       <c r="E53" t="s">
         <v>14</v>
       </c>
-      <c r="I53" s="19"/>
+      <c r="I53" s="18"/>
     </row>
     <row r="54" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="3">
         <v>48</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C54" t="s">
-        <v>71</v>
-      </c>
-      <c r="D54" s="9">
+        <v>68</v>
+      </c>
+      <c r="D54" s="8">
         <v>53</v>
       </c>
       <c r="E54" t="s">
         <v>14</v>
       </c>
-      <c r="I54" s="19"/>
+      <c r="I54" s="18"/>
     </row>
     <row r="55" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="3">
         <v>49</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="D55" s="9">
+        <v>98</v>
+      </c>
+      <c r="D55" s="8">
         <v>54</v>
       </c>
       <c r="E55" t="s">
         <v>14</v>
       </c>
-      <c r="I55" s="19"/>
+      <c r="I55" s="18"/>
     </row>
     <row r="56" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="3">
         <v>55</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="D56" s="9">
+        <v>102</v>
+      </c>
+      <c r="D56" s="8">
         <v>55</v>
       </c>
       <c r="E56" t="s">
         <v>14</v>
       </c>
-      <c r="I56" s="19"/>
+      <c r="I56" s="18"/>
     </row>
     <row r="57" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="3">
         <v>59</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="D57" s="9">
+        <v>104</v>
+      </c>
+      <c r="D57" s="8">
         <v>56</v>
       </c>
       <c r="E57" t="s">
         <v>14</v>
       </c>
-      <c r="I57" s="19"/>
+      <c r="I57" s="18"/>
     </row>
     <row r="58" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="3">
         <v>66</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="D58" s="9">
+        <v>110</v>
+      </c>
+      <c r="D58" s="8">
         <v>57</v>
       </c>
       <c r="E58" t="s">
         <v>14</v>
       </c>
-      <c r="I58" s="19"/>
+      <c r="I58" s="18"/>
     </row>
     <row r="59" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="3">
         <v>70</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="D59" s="9">
+        <v>113</v>
+      </c>
+      <c r="D59" s="8">
         <v>58</v>
       </c>
       <c r="E59" t="s">
         <v>14</v>
       </c>
-      <c r="I59" s="19"/>
+      <c r="I59" s="18"/>
     </row>
     <row r="60" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="3">
         <v>74</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C60" t="s">
-        <v>71</v>
-      </c>
-      <c r="D60" s="9">
+        <v>68</v>
+      </c>
+      <c r="D60" s="8">
         <v>59</v>
       </c>
       <c r="E60" t="s">
         <v>14</v>
       </c>
-      <c r="I60" s="19"/>
+      <c r="I60" s="18"/>
     </row>
     <row r="61" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="1">
         <v>143</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C61" t="s">
         <v>13</v>
       </c>
-      <c r="D61" s="9">
+      <c r="D61" s="8">
         <v>60</v>
       </c>
       <c r="E61" t="s">
         <v>14</v>
       </c>
-      <c r="I61" s="19"/>
+      <c r="I61" s="18"/>
     </row>
     <row r="62" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="3">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="D62" s="9">
+        <v>123</v>
+      </c>
+      <c r="D62" s="8">
         <v>61</v>
       </c>
       <c r="E62" t="s">
         <v>14</v>
       </c>
-      <c r="I62" s="19"/>
+      <c r="I62" s="18"/>
     </row>
     <row r="63" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="3">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="D63" s="9">
+        <v>125</v>
+      </c>
+      <c r="D63" s="8">
         <v>62</v>
       </c>
       <c r="E63" t="s">
         <v>14</v>
       </c>
-      <c r="I63" s="19"/>
+      <c r="I63" s="18"/>
     </row>
     <row r="64" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="3">
-        <v>87</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="D64" s="9">
+        <v>34</v>
+      </c>
+      <c r="B64" s="21" t="s">
+        <v>145</v>
+      </c>
+      <c r="D64" s="8">
         <v>63</v>
       </c>
       <c r="E64" t="s">
-        <v>14</v>
-      </c>
-      <c r="I64" s="19"/>
+        <v>6</v>
+      </c>
+      <c r="I64" s="18"/>
     </row>
     <row r="65" spans="1:9" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="3">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="D65" s="9">
+        <v>96</v>
+      </c>
+      <c r="C65" t="s">
+        <v>68</v>
+      </c>
+      <c r="D65" s="8">
         <v>64</v>
       </c>
       <c r="E65" t="s">
-        <v>14</v>
-      </c>
-      <c r="I65" s="19"/>
+        <v>6</v>
+      </c>
+      <c r="I65" s="18"/>
     </row>
     <row r="66" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="3">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="C66" t="s">
-        <v>71</v>
-      </c>
-      <c r="D66" s="9">
+        <v>101</v>
+      </c>
+      <c r="D66" s="8">
         <v>65</v>
       </c>
       <c r="E66" t="s">
         <v>6</v>
       </c>
-      <c r="I66" s="19"/>
+      <c r="I66" s="18"/>
     </row>
     <row r="67" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="3">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="D67" s="9">
+        <v>105</v>
+      </c>
+      <c r="D67" s="8">
         <v>66</v>
       </c>
       <c r="E67" t="s">
         <v>6</v>
       </c>
-      <c r="I67" s="19"/>
+      <c r="I67" s="18"/>
     </row>
     <row r="68" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="3">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="D68" s="9">
+      <c r="D68" s="8">
         <v>67</v>
       </c>
       <c r="E68" t="s">
         <v>6</v>
       </c>
-      <c r="I68" s="19"/>
+      <c r="I68" s="18"/>
     </row>
     <row r="69" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A69" s="3">
-        <v>65</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="D69" s="9">
+      <c r="A69" s="2">
+        <v>103</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D69" s="8">
         <v>68</v>
       </c>
       <c r="E69" t="s">
         <v>6</v>
       </c>
-      <c r="I69" s="19"/>
+      <c r="I69" s="18"/>
     </row>
     <row r="70" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="2">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="D70" s="9">
+        <v>62</v>
+      </c>
+      <c r="D70" s="8">
         <v>69</v>
       </c>
       <c r="E70" t="s">
         <v>6</v>
       </c>
-      <c r="I70" s="19"/>
+      <c r="I70" s="18"/>
     </row>
     <row r="71" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A71" s="2">
-        <v>111</v>
-      </c>
-      <c r="B71" s="2" t="s">
+      <c r="A71" s="3">
         <v>65</v>
       </c>
-      <c r="D71" s="9">
+      <c r="B71" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D71" s="8">
         <v>70</v>
       </c>
       <c r="E71" t="s">
         <v>6</v>
       </c>
-      <c r="I71" s="19"/>
+      <c r="I71" s="18"/>
     </row>
     <row r="72" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="3">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="D72" s="9">
+        <v>119</v>
+      </c>
+      <c r="D72" s="8">
         <v>71</v>
       </c>
       <c r="E72" t="s">
         <v>6</v>
       </c>
-      <c r="I72" s="19"/>
+      <c r="I72" s="18"/>
     </row>
     <row r="73" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="3">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D73" s="9">
+        <v>121</v>
+      </c>
+      <c r="D73" s="8">
         <v>72</v>
       </c>
       <c r="E73" t="s">
         <v>6</v>
       </c>
-      <c r="I73" s="19"/>
+      <c r="I73" s="18"/>
     </row>
     <row r="74" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A74" s="3">
-        <v>79</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="D74" s="9">
+      <c r="A74" s="1">
+        <v>113</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C74" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="D74" s="8">
         <v>73</v>
       </c>
       <c r="E74" t="s">
         <v>6</v>
       </c>
-      <c r="I74" s="19"/>
+      <c r="I74" s="18"/>
     </row>
     <row r="75" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="3">
-        <v>81</v>
+        <v>53</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="D75" s="9">
+        <v>100</v>
+      </c>
+      <c r="D75" s="8">
         <v>74</v>
       </c>
       <c r="E75" t="s">
         <v>6</v>
       </c>
-      <c r="I75" s="19"/>
+      <c r="I75" s="18"/>
     </row>
     <row r="76" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A76" s="1">
-        <v>113</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C76" s="14" t="s">
-        <v>144</v>
-      </c>
-      <c r="D76" s="9">
+      <c r="A76" s="3">
+        <v>7</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D76" s="8">
         <v>75</v>
       </c>
       <c r="E76" t="s">
         <v>6</v>
       </c>
-      <c r="I76" s="19"/>
+      <c r="I76" s="18"/>
     </row>
     <row r="77" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="3">
-        <v>53</v>
+        <v>8</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="D77" s="9">
+        <v>70</v>
+      </c>
+      <c r="D77" s="8">
         <v>76</v>
       </c>
       <c r="E77" t="s">
         <v>6</v>
       </c>
-      <c r="I77" s="19"/>
+      <c r="I77" s="18"/>
     </row>
     <row r="78" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="3">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D78" s="9">
+        <v>81</v>
+      </c>
+      <c r="D78" s="8">
         <v>77</v>
       </c>
       <c r="E78" t="s">
         <v>6</v>
       </c>
-      <c r="I78" s="19"/>
+      <c r="I78" s="18"/>
     </row>
     <row r="79" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="3">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="D79" s="9">
+        <v>78</v>
+      </c>
+      <c r="D79" s="8">
         <v>78</v>
       </c>
       <c r="E79" t="s">
         <v>6</v>
       </c>
-      <c r="I79" s="19"/>
+      <c r="I79" s="18"/>
     </row>
     <row r="80" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="3">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B80" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="D80" s="9">
+      <c r="D80" s="8">
         <v>79</v>
       </c>
       <c r="E80" t="s">
         <v>6</v>
       </c>
-      <c r="I80" s="19"/>
+      <c r="I80" s="18"/>
     </row>
     <row r="81" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A81" s="3">
-        <v>24</v>
-      </c>
-      <c r="B81" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="D81" s="9">
+      <c r="A81" s="2">
+        <v>136</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D81" s="8">
         <v>80</v>
       </c>
       <c r="E81" t="s">
+        <v>4</v>
+      </c>
+      <c r="I81" s="18"/>
+    </row>
+    <row r="82" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A82" s="3">
+        <v>72</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D82" s="8">
+        <v>81</v>
+      </c>
+      <c r="E82" t="s">
         <v>6</v>
       </c>
-      <c r="I81" s="19"/>
-    </row>
-    <row r="82" spans="1:9" s="4" customFormat="1" ht="13" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="7"/>
-      <c r="B82" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="C82" s="7"/>
-      <c r="D82" s="10" t="s">
-        <v>142</v>
-      </c>
-      <c r="E82" s="7"/>
-      <c r="F82" s="7"/>
-      <c r="G82" s="7"/>
-      <c r="H82" s="7"/>
-      <c r="I82" s="20"/>
+      <c r="I82" s="18"/>
     </row>
     <row r="83" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A83" s="3">
+        <v>82</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D83" s="8">
+        <v>82</v>
+      </c>
+      <c r="E83" t="s">
+        <v>14</v>
+      </c>
+      <c r="I83" s="18"/>
+    </row>
+    <row r="84" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A84" s="3">
+        <v>80</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D84" s="8">
+        <v>83</v>
+      </c>
+      <c r="E84" t="s">
+        <v>14</v>
+      </c>
+      <c r="I84" s="18"/>
+    </row>
+    <row r="85" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A85" s="3">
+        <v>61</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="C85" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="D85" s="8">
+        <v>84</v>
+      </c>
+      <c r="E85" t="s">
+        <v>14</v>
+      </c>
+      <c r="I85" s="18"/>
+    </row>
+    <row r="86" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A86" s="3">
+        <v>56</v>
+      </c>
+      <c r="B86" s="21" t="s">
+        <v>143</v>
+      </c>
+      <c r="D86" s="8">
+        <v>85</v>
+      </c>
+      <c r="E86" t="s">
+        <v>1</v>
+      </c>
+      <c r="I86" s="18"/>
+    </row>
+    <row r="87" spans="1:9" s="4" customFormat="1" ht="13" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A87" s="6"/>
+      <c r="B87" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="C87" s="6"/>
+      <c r="D87" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="E87" s="6"/>
+      <c r="F87" s="6"/>
+      <c r="G87" s="6"/>
+      <c r="H87" s="6"/>
+      <c r="I87" s="19"/>
+    </row>
+    <row r="88" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A88" s="3">
         <v>31</v>
       </c>
-      <c r="B83" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D83" s="9">
+      <c r="B88" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D88" s="8">
         <v>89</v>
-      </c>
-      <c r="E83" t="s">
-        <v>6</v>
-      </c>
-      <c r="I83" s="15" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="84" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A84" s="2">
-        <v>58</v>
-      </c>
-      <c r="B84" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D84" s="9">
-        <v>90</v>
-      </c>
-      <c r="E84" t="s">
-        <v>6</v>
-      </c>
-      <c r="I84" s="16"/>
-    </row>
-    <row r="85" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A85" s="2">
-        <v>72</v>
-      </c>
-      <c r="B85" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D85" s="9">
-        <v>91</v>
-      </c>
-      <c r="E85" t="s">
-        <v>6</v>
-      </c>
-      <c r="I85" s="16"/>
-    </row>
-    <row r="86" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A86" s="1">
-        <v>122</v>
-      </c>
-      <c r="B86" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C86" t="s">
-        <v>13</v>
-      </c>
-      <c r="D86" s="9">
-        <v>92</v>
-      </c>
-      <c r="E86" t="s">
-        <v>6</v>
-      </c>
-      <c r="I86" s="16"/>
-    </row>
-    <row r="87" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A87" s="1">
-        <v>132</v>
-      </c>
-      <c r="B87" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C87" t="s">
-        <v>13</v>
-      </c>
-      <c r="D87" s="9">
-        <v>93</v>
-      </c>
-      <c r="E87" t="s">
-        <v>6</v>
-      </c>
-      <c r="I87" s="16"/>
-    </row>
-    <row r="88" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A88" s="1">
-        <v>61</v>
-      </c>
-      <c r="B88" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D88" s="9">
-        <v>94</v>
       </c>
       <c r="E88" t="s">
         <v>6</v>
       </c>
-      <c r="I88" s="16"/>
+      <c r="I88" s="14" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="89" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A89" s="1">
-        <v>38</v>
-      </c>
-      <c r="B89" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D89" s="9">
-        <v>95</v>
+      <c r="A89" s="2">
+        <v>58</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D89" s="8">
+        <v>90</v>
       </c>
       <c r="E89" t="s">
         <v>6</v>
       </c>
-      <c r="I89" s="16"/>
+      <c r="I89" s="15"/>
     </row>
     <row r="90" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A90" s="1">
-        <v>24</v>
-      </c>
-      <c r="B90" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D90" s="9">
-        <v>96</v>
+      <c r="A90" s="3">
+        <v>50</v>
+      </c>
+      <c r="B90" s="22" t="s">
+        <v>144</v>
+      </c>
+      <c r="D90" s="8">
+        <v>91</v>
       </c>
       <c r="E90" t="s">
         <v>6</v>
       </c>
-      <c r="I90" s="16"/>
+      <c r="I90" s="15"/>
     </row>
     <row r="91" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A91" s="3">
-        <v>44</v>
-      </c>
-      <c r="B91" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="D91" s="9">
-        <v>97</v>
+      <c r="A91" s="1">
+        <v>122</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C91" t="s">
+        <v>13</v>
+      </c>
+      <c r="D91" s="8">
+        <v>92</v>
       </c>
       <c r="E91" t="s">
         <v>6</v>
       </c>
-      <c r="I91" s="16"/>
+      <c r="I91" s="15"/>
     </row>
     <row r="92" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A92" s="3">
-        <v>46</v>
-      </c>
-      <c r="B92" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="D92" s="9">
-        <v>98</v>
+      <c r="A92" s="1">
+        <v>132</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C92" t="s">
+        <v>13</v>
+      </c>
+      <c r="D92" s="8">
+        <v>93</v>
       </c>
       <c r="E92" t="s">
         <v>6</v>
       </c>
-      <c r="I92" s="16"/>
+      <c r="I92" s="15"/>
     </row>
     <row r="93" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A93" s="1">
-        <v>137</v>
+        <v>61</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C93" t="s">
-        <v>13</v>
-      </c>
-      <c r="D93" s="9">
-        <v>99</v>
+        <v>20</v>
+      </c>
+      <c r="D93" s="8">
+        <v>94</v>
       </c>
       <c r="E93" t="s">
-        <v>1</v>
-      </c>
-      <c r="I93" s="16"/>
+        <v>6</v>
+      </c>
+      <c r="I93" s="15"/>
     </row>
     <row r="94" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A94" s="1">
-        <v>139</v>
+        <v>38</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D94" s="9">
-        <v>100</v>
+        <v>9</v>
+      </c>
+      <c r="D94" s="8">
+        <v>95</v>
       </c>
       <c r="E94" t="s">
-        <v>1</v>
-      </c>
-      <c r="I94" s="16"/>
+        <v>6</v>
+      </c>
+      <c r="I94" s="15"/>
     </row>
     <row r="95" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A95" s="1">
+        <v>24</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D95" s="8">
+        <v>96</v>
+      </c>
+      <c r="E95" t="s">
+        <v>6</v>
+      </c>
+      <c r="I95" s="15"/>
+    </row>
+    <row r="96" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A96" s="3">
+        <v>44</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D96" s="8">
+        <v>97</v>
+      </c>
+      <c r="E96" t="s">
+        <v>6</v>
+      </c>
+      <c r="I96" s="15"/>
+    </row>
+    <row r="97" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A97" s="3">
+        <v>46</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D97" s="8">
+        <v>98</v>
+      </c>
+      <c r="E97" t="s">
+        <v>6</v>
+      </c>
+      <c r="I97" s="15"/>
+    </row>
+    <row r="98" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A98" s="1">
+        <v>137</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C98" t="s">
+        <v>13</v>
+      </c>
+      <c r="D98" s="8">
+        <v>99</v>
+      </c>
+      <c r="E98" t="s">
+        <v>1</v>
+      </c>
+      <c r="I98" s="15"/>
+    </row>
+    <row r="99" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A99" s="1">
+        <v>139</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D99" s="8">
+        <v>100</v>
+      </c>
+      <c r="E99" t="s">
+        <v>1</v>
+      </c>
+      <c r="I99" s="15"/>
+    </row>
+    <row r="100" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A100" s="1">
         <v>141</v>
       </c>
-      <c r="B95" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D95" s="9">
+      <c r="B100" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D100" s="8">
         <v>101</v>
       </c>
-      <c r="E95" t="s">
-        <v>1</v>
-      </c>
-      <c r="I95" s="16"/>
-    </row>
-    <row r="96" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A96" s="1">
+      <c r="E100" t="s">
+        <v>1</v>
+      </c>
+      <c r="I100" s="15"/>
+    </row>
+    <row r="101" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A101" s="1">
         <v>16</v>
       </c>
-      <c r="B96" s="1" t="s">
+      <c r="B101" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D96" s="9">
+      <c r="D101" s="8">
         <v>102</v>
       </c>
-      <c r="E96" t="s">
-        <v>1</v>
-      </c>
-      <c r="I96" s="16"/>
-    </row>
-    <row r="97" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A97" s="1">
+      <c r="E101" t="s">
+        <v>1</v>
+      </c>
+      <c r="I101" s="15"/>
+    </row>
+    <row r="102" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A102" s="1">
         <v>72</v>
       </c>
-      <c r="B97" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C97" t="s">
+      <c r="B102" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C102" t="s">
         <v>13</v>
       </c>
-      <c r="D97" s="9">
+      <c r="D102" s="8">
         <v>104</v>
       </c>
-      <c r="E97" t="s">
-        <v>1</v>
-      </c>
-      <c r="I97" s="16"/>
-    </row>
-    <row r="98" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A98" s="2">
+      <c r="E102" t="s">
+        <v>1</v>
+      </c>
+      <c r="I102" s="15"/>
+    </row>
+    <row r="103" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A103" s="2">
         <v>47</v>
       </c>
-      <c r="B98" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D98" s="9">
+      <c r="B103" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D103" s="8">
         <v>103</v>
       </c>
-      <c r="E98" t="s">
-        <v>1</v>
-      </c>
-      <c r="I98" s="16"/>
-    </row>
-    <row r="99" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A99" s="3">
+      <c r="E103" t="s">
+        <v>1</v>
+      </c>
+      <c r="I103" s="15"/>
+    </row>
+    <row r="104" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A104" s="3">
         <v>17</v>
       </c>
-      <c r="B99" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="D99" s="9">
+      <c r="B104" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D104" s="8">
         <v>105</v>
       </c>
-      <c r="E99" t="s">
-        <v>1</v>
-      </c>
-      <c r="I99" s="16"/>
-    </row>
-    <row r="100" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A100" s="3">
+      <c r="E104" t="s">
+        <v>1</v>
+      </c>
+      <c r="I104" s="15"/>
+    </row>
+    <row r="105" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A105" s="3">
         <v>18</v>
       </c>
-      <c r="B100" s="3" t="s">
+      <c r="B105" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D105" s="8">
+        <v>106</v>
+      </c>
+      <c r="E105" t="s">
+        <v>1</v>
+      </c>
+      <c r="I105" s="15"/>
+    </row>
+    <row r="106" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A106" s="3">
+        <v>21</v>
+      </c>
+      <c r="B106" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D100" s="9">
-        <v>106</v>
-      </c>
-      <c r="E100" t="s">
-        <v>1</v>
-      </c>
-      <c r="I100" s="16"/>
-    </row>
-    <row r="101" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A101" s="3">
+      <c r="D106" s="8">
+        <v>107</v>
+      </c>
+      <c r="E106" t="s">
+        <v>1</v>
+      </c>
+      <c r="I106" s="15"/>
+    </row>
+    <row r="107" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A107" s="3">
+        <v>23</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D107" s="8">
+        <v>108</v>
+      </c>
+      <c r="E107" t="s">
+        <v>1</v>
+      </c>
+      <c r="I107" s="15"/>
+    </row>
+    <row r="108" spans="1:9" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A108" s="1">
+        <v>65</v>
+      </c>
+      <c r="B108" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B101" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D101" s="9">
-        <v>107</v>
-      </c>
-      <c r="E101" t="s">
-        <v>1</v>
-      </c>
-      <c r="I101" s="16"/>
-    </row>
-    <row r="102" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A102" s="3">
-        <v>23</v>
-      </c>
-      <c r="B102" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="D102" s="9">
-        <v>108</v>
-      </c>
-      <c r="E102" t="s">
-        <v>1</v>
-      </c>
-      <c r="I102" s="16"/>
-    </row>
-    <row r="103" spans="1:9" ht="14" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A103" s="1">
-        <v>65</v>
-      </c>
-      <c r="B103" s="1" t="s">
+      <c r="D108" s="8">
+        <v>109</v>
+      </c>
+      <c r="E108" t="s">
+        <v>1</v>
+      </c>
+      <c r="I108" s="15"/>
+    </row>
+    <row r="109" spans="1:9" s="4" customFormat="1" ht="13" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A109" s="12">
+        <v>70</v>
+      </c>
+      <c r="B109" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="D103" s="9">
-        <v>109</v>
-      </c>
-      <c r="E103" t="s">
-        <v>1</v>
-      </c>
-      <c r="I103" s="16"/>
-    </row>
-    <row r="104" spans="1:9" s="4" customFormat="1" ht="13" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A104" s="13">
-        <v>70</v>
-      </c>
-      <c r="B104" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="D104" s="8">
+      <c r="D109" s="7">
         <v>110</v>
       </c>
-      <c r="E104" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="I104" s="17"/>
-    </row>
-    <row r="105" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A105" s="1">
+      <c r="E109" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="I109" s="16"/>
+    </row>
+    <row r="110" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A110" s="1">
         <v>80</v>
       </c>
-      <c r="B105" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D105" s="9">
+      <c r="B110" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D110" s="8">
         <v>111</v>
       </c>
-      <c r="E105" t="s">
-        <v>1</v>
-      </c>
-      <c r="I105" s="18" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="106" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A106" s="1">
-        <v>86</v>
-      </c>
-      <c r="B106" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D106" s="9">
-        <v>112</v>
-      </c>
-      <c r="E106" t="s">
-        <v>1</v>
-      </c>
-      <c r="I106" s="19"/>
-    </row>
-    <row r="107" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A107" s="2">
-        <v>47</v>
-      </c>
-      <c r="B107" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D107" s="9">
-        <v>113</v>
-      </c>
-      <c r="E107" t="s">
-        <v>1</v>
-      </c>
-      <c r="I107" s="19"/>
-    </row>
-    <row r="108" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A108" s="3">
-        <v>29</v>
-      </c>
-      <c r="B108" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="D108" s="9">
-        <v>114</v>
-      </c>
-      <c r="E108" t="s">
-        <v>1</v>
-      </c>
-      <c r="I108" s="19"/>
-    </row>
-    <row r="109" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A109" s="3">
-        <v>30</v>
-      </c>
-      <c r="B109" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="D109" s="9">
-        <v>115</v>
-      </c>
-      <c r="E109" t="s">
-        <v>1</v>
-      </c>
-      <c r="I109" s="19"/>
-    </row>
-    <row r="110" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A110" s="3">
-        <v>36</v>
-      </c>
-      <c r="B110" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="D110" s="9">
-        <v>116</v>
-      </c>
       <c r="E110" t="s">
         <v>1</v>
       </c>
-      <c r="I110" s="19"/>
+      <c r="I110" s="17" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="111" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A111" s="1">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D111" s="9">
-        <v>117</v>
+        <v>27</v>
+      </c>
+      <c r="D111" s="8">
+        <v>112</v>
       </c>
       <c r="E111" t="s">
         <v>1</v>
       </c>
-      <c r="I111" s="19"/>
+      <c r="I111" s="18"/>
     </row>
     <row r="112" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A112" s="1">
-        <v>40</v>
-      </c>
-      <c r="B112" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D112" s="9">
-        <v>118</v>
+      <c r="A112" s="2">
+        <v>47</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D112" s="8">
+        <v>113</v>
       </c>
       <c r="E112" t="s">
         <v>1</v>
       </c>
-      <c r="I112" s="19"/>
+      <c r="I112" s="18"/>
     </row>
     <row r="113" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A113" s="1">
-        <v>51</v>
-      </c>
-      <c r="B113" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D113" s="9">
-        <v>119</v>
+      <c r="A113" s="3">
+        <v>29</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D113" s="8">
+        <v>114</v>
       </c>
       <c r="E113" t="s">
         <v>1</v>
       </c>
-      <c r="I113" s="19"/>
+      <c r="I113" s="18"/>
     </row>
     <row r="114" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A114" s="1">
-        <v>59</v>
-      </c>
-      <c r="B114" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D114" s="9">
-        <v>120</v>
+      <c r="A114" s="3">
+        <v>30</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D114" s="8">
+        <v>115</v>
       </c>
       <c r="E114" t="s">
         <v>1</v>
       </c>
-      <c r="I114" s="19"/>
+      <c r="I114" s="18"/>
     </row>
     <row r="115" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A115" s="1">
-        <v>89</v>
-      </c>
-      <c r="B115" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C115" t="s">
-        <v>13</v>
-      </c>
-      <c r="D115" s="9">
-        <v>121</v>
+      <c r="A115" s="3">
+        <v>36</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D115" s="8">
+        <v>116</v>
       </c>
       <c r="E115" t="s">
         <v>1</v>
       </c>
-      <c r="I115" s="19"/>
+      <c r="I115" s="18"/>
     </row>
     <row r="116" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A116" s="1">
-        <v>105</v>
+        <v>21</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D116" s="9">
-        <v>122</v>
+        <v>2</v>
+      </c>
+      <c r="D116" s="8">
+        <v>117</v>
       </c>
       <c r="E116" t="s">
         <v>1</v>
       </c>
-      <c r="I116" s="19"/>
+      <c r="I116" s="18"/>
     </row>
     <row r="117" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A117" s="1">
-        <v>116</v>
+        <v>40</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D117" s="9">
-        <v>123</v>
+        <v>10</v>
+      </c>
+      <c r="D117" s="8">
+        <v>118</v>
       </c>
       <c r="E117" t="s">
         <v>1</v>
       </c>
-      <c r="I117" s="19"/>
+      <c r="I117" s="18"/>
     </row>
     <row r="118" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A118" s="1">
-        <v>117</v>
+        <v>51</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D118" s="9">
-        <v>124</v>
+        <v>17</v>
+      </c>
+      <c r="D118" s="8">
+        <v>119</v>
       </c>
       <c r="E118" t="s">
         <v>1</v>
       </c>
-      <c r="I118" s="19"/>
+      <c r="I118" s="18"/>
     </row>
     <row r="119" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A119" s="1">
-        <v>124</v>
+        <v>59</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C119" s="14" t="s">
-        <v>144</v>
-      </c>
-      <c r="D119" s="9">
-        <v>125</v>
+        <v>18</v>
+      </c>
+      <c r="D119" s="8">
+        <v>120</v>
       </c>
       <c r="E119" t="s">
         <v>1</v>
       </c>
-      <c r="I119" s="19"/>
+      <c r="I119" s="18"/>
     </row>
     <row r="120" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A120" s="1">
+        <v>89</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C120" t="s">
+        <v>13</v>
+      </c>
+      <c r="D120" s="8">
+        <v>121</v>
+      </c>
+      <c r="E120" t="s">
+        <v>1</v>
+      </c>
+      <c r="I120" s="18"/>
+    </row>
+    <row r="121" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A121" s="1">
+        <v>105</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D121" s="8">
+        <v>122</v>
+      </c>
+      <c r="E121" t="s">
+        <v>1</v>
+      </c>
+      <c r="I121" s="18"/>
+    </row>
+    <row r="122" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A122" s="1">
+        <v>116</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D122" s="8">
+        <v>123</v>
+      </c>
+      <c r="E122" t="s">
+        <v>1</v>
+      </c>
+      <c r="I122" s="18"/>
+    </row>
+    <row r="123" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A123" s="1">
+        <v>117</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D123" s="8">
+        <v>124</v>
+      </c>
+      <c r="E123" t="s">
+        <v>1</v>
+      </c>
+      <c r="I123" s="18"/>
+    </row>
+    <row r="124" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A124" s="1">
+        <v>124</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C124" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="D124" s="8">
+        <v>125</v>
+      </c>
+      <c r="E124" t="s">
+        <v>1</v>
+      </c>
+      <c r="I124" s="18"/>
+    </row>
+    <row r="125" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A125" s="1">
         <v>128</v>
       </c>
-      <c r="B120" s="1" t="s">
+      <c r="B125" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D125" s="8">
+        <v>126</v>
+      </c>
+      <c r="E125" t="s">
+        <v>1</v>
+      </c>
+      <c r="I125" s="18"/>
+    </row>
+    <row r="126" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A126" s="2">
+        <v>102</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D126" s="8">
+        <v>127</v>
+      </c>
+      <c r="E126" t="s">
+        <v>1</v>
+      </c>
+      <c r="I126" s="18"/>
+    </row>
+    <row r="127" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A127" s="3">
+        <v>42</v>
+      </c>
+      <c r="B127" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D127" s="8">
+        <v>128</v>
+      </c>
+      <c r="E127" t="s">
+        <v>1</v>
+      </c>
+      <c r="I127" s="18"/>
+    </row>
+    <row r="128" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A128" s="3">
+        <v>52</v>
+      </c>
+      <c r="B128" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D128" s="8">
+        <v>129</v>
+      </c>
+      <c r="E128" t="s">
+        <v>1</v>
+      </c>
+      <c r="I128" s="18"/>
+    </row>
+    <row r="129" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A129" s="3">
+        <v>86</v>
+      </c>
+      <c r="B129" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C129" t="s">
+        <v>68</v>
+      </c>
+      <c r="D129" s="8">
+        <v>130</v>
+      </c>
+      <c r="E129" t="s">
+        <v>1</v>
+      </c>
+      <c r="I129" s="18"/>
+    </row>
+    <row r="130" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A130" s="2">
+        <v>135</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D130" s="8">
+        <v>131</v>
+      </c>
+      <c r="E130" t="s">
+        <v>1</v>
+      </c>
+      <c r="I130" s="18"/>
+    </row>
+    <row r="131" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A131" s="3">
+        <v>6</v>
+      </c>
+      <c r="B131" s="21" t="s">
+        <v>141</v>
+      </c>
+      <c r="C131" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="D131" s="8">
+        <v>132</v>
+      </c>
+      <c r="E131" t="s">
+        <v>1</v>
+      </c>
+      <c r="I131" s="18"/>
+    </row>
+    <row r="132" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A132" s="3">
         <v>43</v>
       </c>
-      <c r="D120" s="9">
-        <v>126</v>
-      </c>
-      <c r="E120" t="s">
-        <v>1</v>
-      </c>
-      <c r="I120" s="19"/>
-    </row>
-    <row r="121" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A121" s="2">
-        <v>102</v>
-      </c>
-      <c r="B121" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D121" s="9">
-        <v>127</v>
-      </c>
-      <c r="E121" t="s">
-        <v>1</v>
-      </c>
-      <c r="I121" s="19"/>
-    </row>
-    <row r="122" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A122" s="3">
-        <v>42</v>
-      </c>
-      <c r="B122" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="D122" s="9">
-        <v>128</v>
-      </c>
-      <c r="E122" t="s">
-        <v>1</v>
-      </c>
-      <c r="I122" s="19"/>
-    </row>
-    <row r="123" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A123" s="3">
-        <v>52</v>
-      </c>
-      <c r="B123" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="D123" s="9">
-        <v>129</v>
-      </c>
-      <c r="E123" t="s">
-        <v>1</v>
-      </c>
-      <c r="I123" s="19"/>
-    </row>
-    <row r="124" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A124" s="3">
-        <v>86</v>
-      </c>
-      <c r="B124" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="C124" t="s">
-        <v>71</v>
-      </c>
-      <c r="D124" s="9">
-        <v>130</v>
-      </c>
-      <c r="E124" t="s">
-        <v>1</v>
-      </c>
-      <c r="I124" s="19"/>
-    </row>
-    <row r="125" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A125" s="2">
-        <v>135</v>
-      </c>
-      <c r="B125" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D125" s="9">
-        <v>131</v>
-      </c>
-      <c r="E125" t="s">
-        <v>1</v>
-      </c>
-      <c r="I125" s="19"/>
-    </row>
-    <row r="126" spans="1:9" s="4" customFormat="1" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A126" s="7"/>
-      <c r="B126" s="7" t="s">
+      <c r="B132" s="21" t="s">
+        <v>142</v>
+      </c>
+      <c r="D132" s="8">
+        <v>133</v>
+      </c>
+      <c r="E132" t="s">
+        <v>1</v>
+      </c>
+      <c r="I132" s="18"/>
+    </row>
+    <row r="133" spans="1:9" s="4" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A133" s="6"/>
+      <c r="B133" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="C133" s="6"/>
+      <c r="D133" s="9">
+        <v>134</v>
+      </c>
+      <c r="E133" s="6"/>
+      <c r="F133" s="6"/>
+      <c r="G133" s="6"/>
+      <c r="H133" s="6"/>
+      <c r="I133" s="19"/>
+    </row>
+    <row r="135" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A135" s="1"/>
+      <c r="B135" s="10" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A136" s="2"/>
+      <c r="B136" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="C126" s="7"/>
-      <c r="D126" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="E126" s="7"/>
-      <c r="F126" s="7"/>
-      <c r="G126" s="7"/>
-      <c r="H126" s="7"/>
-      <c r="I126" s="20"/>
-    </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A128" s="1"/>
-      <c r="B128" s="11" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A129" s="2"/>
-      <c r="B129" s="11" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A130" s="3"/>
-      <c r="B130" s="11" t="s">
-        <v>141</v>
+    </row>
+    <row r="137" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A137" s="3"/>
+      <c r="B137" s="10" t="s">
+        <v>138</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E125">
-    <sortCondition ref="D1:D125"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E130">
+    <sortCondition ref="D1:D130"/>
   </sortState>
   <mergeCells count="4">
     <mergeCell ref="I2:I45"/>
-    <mergeCell ref="I46:I82"/>
-    <mergeCell ref="I105:I126"/>
-    <mergeCell ref="I83:I104"/>
+    <mergeCell ref="I46:I87"/>
+    <mergeCell ref="I110:I133"/>
+    <mergeCell ref="I88:I109"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/STAIX2026/assets/Poster-Presentation-Label-Assignment.xlsx
+++ b/STAIX2026/assets/Poster-Presentation-Label-Assignment.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tracyke/Dropbox/Mac (2)/Documents/2026/STAI-X conference/Poster session/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B21276E5-A52B-1040-B89A-1D24086F1E8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E07E6659-BFEC-D046-878E-7CCBF2DA6420}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9000" yWindow="4080" windowWidth="38400" windowHeight="19240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="500" windowWidth="38400" windowHeight="19240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Assignment" sheetId="7" r:id="rId1"/>
@@ -600,7 +600,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
@@ -617,6 +617,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -635,13 +638,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1171,7 +1167,7 @@
       <c r="E2" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="14" t="s">
+      <c r="I2" s="17" t="s">
         <v>131</v>
       </c>
     </row>
@@ -1188,7 +1184,7 @@
       <c r="E3" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="15"/>
+      <c r="I3" s="18"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A4" s="1">
@@ -1206,7 +1202,7 @@
       <c r="E4" t="s">
         <v>4</v>
       </c>
-      <c r="I4" s="15"/>
+      <c r="I4" s="18"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A5" s="2">
@@ -1221,7 +1217,7 @@
       <c r="E5" t="s">
         <v>4</v>
       </c>
-      <c r="I5" s="15"/>
+      <c r="I5" s="18"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A6" s="2">
@@ -1236,7 +1232,7 @@
       <c r="E6" t="s">
         <v>4</v>
       </c>
-      <c r="I6" s="15"/>
+      <c r="I6" s="18"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A7" s="3">
@@ -1251,7 +1247,7 @@
       <c r="E7" t="s">
         <v>4</v>
       </c>
-      <c r="I7" s="15"/>
+      <c r="I7" s="18"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A8" s="3">
@@ -1266,7 +1262,7 @@
       <c r="E8" t="s">
         <v>4</v>
       </c>
-      <c r="I8" s="15"/>
+      <c r="I8" s="18"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A9" s="3">
@@ -1281,7 +1277,7 @@
       <c r="E9" t="s">
         <v>4</v>
       </c>
-      <c r="I9" s="15"/>
+      <c r="I9" s="18"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A10" s="3">
@@ -1296,7 +1292,7 @@
       <c r="E10" t="s">
         <v>4</v>
       </c>
-      <c r="I10" s="15"/>
+      <c r="I10" s="18"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A11" s="1">
@@ -1311,7 +1307,7 @@
       <c r="E11" t="s">
         <v>4</v>
       </c>
-      <c r="I11" s="15"/>
+      <c r="I11" s="18"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A12" s="1">
@@ -1329,7 +1325,7 @@
       <c r="E12" t="s">
         <v>4</v>
       </c>
-      <c r="I12" s="15"/>
+      <c r="I12" s="18"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A13" s="3">
@@ -1344,7 +1340,7 @@
       <c r="E13" t="s">
         <v>4</v>
       </c>
-      <c r="I13" s="15"/>
+      <c r="I13" s="18"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A14" s="3">
@@ -1359,7 +1355,7 @@
       <c r="E14" t="s">
         <v>4</v>
       </c>
-      <c r="I14" s="15"/>
+      <c r="I14" s="18"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A15" s="3">
@@ -1374,7 +1370,7 @@
       <c r="E15" t="s">
         <v>4</v>
       </c>
-      <c r="I15" s="15"/>
+      <c r="I15" s="18"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A16" s="3">
@@ -1389,7 +1385,7 @@
       <c r="E16" t="s">
         <v>4</v>
       </c>
-      <c r="I16" s="15"/>
+      <c r="I16" s="18"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A17" s="3">
@@ -1404,7 +1400,7 @@
       <c r="E17" t="s">
         <v>4</v>
       </c>
-      <c r="I17" s="15"/>
+      <c r="I17" s="18"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A18" s="1">
@@ -1419,7 +1415,7 @@
       <c r="E18" t="s">
         <v>8</v>
       </c>
-      <c r="I18" s="15"/>
+      <c r="I18" s="18"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A19" s="1">
@@ -1434,7 +1430,7 @@
       <c r="E19" t="s">
         <v>8</v>
       </c>
-      <c r="I19" s="15"/>
+      <c r="I19" s="18"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A20" s="1">
@@ -1449,7 +1445,7 @@
       <c r="E20" t="s">
         <v>8</v>
       </c>
-      <c r="I20" s="15"/>
+      <c r="I20" s="18"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A21" s="2">
@@ -1464,7 +1460,7 @@
       <c r="E21" t="s">
         <v>8</v>
       </c>
-      <c r="I21" s="15"/>
+      <c r="I21" s="18"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A22" s="3">
@@ -1479,7 +1475,7 @@
       <c r="E22" t="s">
         <v>8</v>
       </c>
-      <c r="I22" s="15"/>
+      <c r="I22" s="18"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A23" s="3">
@@ -1494,7 +1490,7 @@
       <c r="E23" t="s">
         <v>8</v>
       </c>
-      <c r="I23" s="15"/>
+      <c r="I23" s="18"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A24" s="3">
@@ -1509,7 +1505,7 @@
       <c r="E24" t="s">
         <v>8</v>
       </c>
-      <c r="I24" s="15"/>
+      <c r="I24" s="18"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A25" s="3">
@@ -1527,7 +1523,7 @@
       <c r="E25" t="s">
         <v>8</v>
       </c>
-      <c r="I25" s="15"/>
+      <c r="I25" s="18"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A26" s="2">
@@ -1542,7 +1538,7 @@
       <c r="E26" t="s">
         <v>8</v>
       </c>
-      <c r="I26" s="15"/>
+      <c r="I26" s="18"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A27" s="1">
@@ -1560,7 +1556,7 @@
       <c r="E27" t="s">
         <v>8</v>
       </c>
-      <c r="I27" s="15"/>
+      <c r="I27" s="18"/>
     </row>
     <row r="28" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="1">
@@ -1575,7 +1571,7 @@
       <c r="E28" t="s">
         <v>8</v>
       </c>
-      <c r="I28" s="15"/>
+      <c r="I28" s="18"/>
     </row>
     <row r="29" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="3">
@@ -1593,7 +1589,7 @@
       <c r="E29" t="s">
         <v>8</v>
       </c>
-      <c r="I29" s="15"/>
+      <c r="I29" s="18"/>
     </row>
     <row r="30" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="3">
@@ -1608,7 +1604,7 @@
       <c r="E30" t="s">
         <v>8</v>
       </c>
-      <c r="I30" s="15"/>
+      <c r="I30" s="18"/>
     </row>
     <row r="31" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="3">
@@ -1623,7 +1619,7 @@
       <c r="E31" t="s">
         <v>8</v>
       </c>
-      <c r="I31" s="15"/>
+      <c r="I31" s="18"/>
     </row>
     <row r="32" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="3">
@@ -1638,7 +1634,7 @@
       <c r="E32" t="s">
         <v>8</v>
       </c>
-      <c r="I32" s="15"/>
+      <c r="I32" s="18"/>
     </row>
     <row r="33" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="2">
@@ -1653,7 +1649,7 @@
       <c r="E33" t="s">
         <v>8</v>
       </c>
-      <c r="I33" s="15"/>
+      <c r="I33" s="18"/>
     </row>
     <row r="34" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="3">
@@ -1668,7 +1664,7 @@
       <c r="E34" t="s">
         <v>14</v>
       </c>
-      <c r="I34" s="15"/>
+      <c r="I34" s="18"/>
     </row>
     <row r="35" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="1">
@@ -1686,7 +1682,7 @@
       <c r="E35" t="s">
         <v>14</v>
       </c>
-      <c r="I35" s="15"/>
+      <c r="I35" s="18"/>
     </row>
     <row r="36" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="1">
@@ -1701,7 +1697,7 @@
       <c r="E36" t="s">
         <v>14</v>
       </c>
-      <c r="I36" s="15"/>
+      <c r="I36" s="18"/>
     </row>
     <row r="37" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="1">
@@ -1716,7 +1712,7 @@
       <c r="E37" t="s">
         <v>14</v>
       </c>
-      <c r="I37" s="15"/>
+      <c r="I37" s="18"/>
     </row>
     <row r="38" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="2">
@@ -1731,7 +1727,7 @@
       <c r="E38" t="s">
         <v>14</v>
       </c>
-      <c r="I38" s="15"/>
+      <c r="I38" s="18"/>
     </row>
     <row r="39" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="2">
@@ -1746,7 +1742,7 @@
       <c r="E39" t="s">
         <v>14</v>
       </c>
-      <c r="I39" s="15"/>
+      <c r="I39" s="18"/>
     </row>
     <row r="40" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="3">
@@ -1764,7 +1760,7 @@
       <c r="E40" t="s">
         <v>14</v>
       </c>
-      <c r="I40" s="15"/>
+      <c r="I40" s="18"/>
     </row>
     <row r="41" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="3">
@@ -1779,7 +1775,7 @@
       <c r="E41" t="s">
         <v>14</v>
       </c>
-      <c r="I41" s="15"/>
+      <c r="I41" s="18"/>
     </row>
     <row r="42" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="3">
@@ -1794,7 +1790,7 @@
       <c r="E42" t="s">
         <v>14</v>
       </c>
-      <c r="I42" s="15"/>
+      <c r="I42" s="18"/>
     </row>
     <row r="43" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="3">
@@ -1809,38 +1805,35 @@
       <c r="E43" t="s">
         <v>14</v>
       </c>
-      <c r="I43" s="15"/>
+      <c r="I43" s="18"/>
     </row>
     <row r="44" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A44" s="23">
+      <c r="A44" s="3">
         <v>37</v>
       </c>
-      <c r="B44" s="23" t="s">
+      <c r="B44" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="C44" s="24"/>
       <c r="D44" s="8">
         <v>43</v>
       </c>
-      <c r="E44" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="F44" s="24"/>
-      <c r="G44" s="24"/>
-      <c r="I44" s="15"/>
+      <c r="E44" t="s">
+        <v>14</v>
+      </c>
+      <c r="I44" s="18"/>
     </row>
     <row r="45" spans="1:9" s="4" customFormat="1" ht="13" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="25"/>
-      <c r="B45" s="25"/>
-      <c r="C45" s="25"/>
-      <c r="D45" s="26">
+      <c r="A45" s="15"/>
+      <c r="B45" s="15"/>
+      <c r="C45" s="15"/>
+      <c r="D45" s="16">
         <v>44</v>
       </c>
-      <c r="E45" s="25"/>
-      <c r="F45" s="25"/>
-      <c r="G45" s="25"/>
-      <c r="H45" s="25"/>
-      <c r="I45" s="16"/>
+      <c r="E45" s="15"/>
+      <c r="F45" s="15"/>
+      <c r="G45" s="15"/>
+      <c r="H45" s="15"/>
+      <c r="I45" s="19"/>
     </row>
     <row r="46" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="3">
@@ -1855,7 +1848,7 @@
       <c r="E46" t="s">
         <v>14</v>
       </c>
-      <c r="I46" s="17" t="s">
+      <c r="I46" s="20" t="s">
         <v>132</v>
       </c>
     </row>
@@ -1872,7 +1865,7 @@
       <c r="E47" t="s">
         <v>14</v>
       </c>
-      <c r="I47" s="18"/>
+      <c r="I47" s="21"/>
     </row>
     <row r="48" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="1">
@@ -1887,13 +1880,13 @@
       <c r="E48" t="s">
         <v>14</v>
       </c>
-      <c r="I48" s="18"/>
+      <c r="I48" s="21"/>
     </row>
     <row r="49" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="1">
         <v>63</v>
       </c>
-      <c r="B49" s="20" t="s">
+      <c r="B49" s="14" t="s">
         <v>140</v>
       </c>
       <c r="D49" s="8">
@@ -1902,7 +1895,7 @@
       <c r="E49" t="s">
         <v>14</v>
       </c>
-      <c r="I49" s="18"/>
+      <c r="I49" s="21"/>
     </row>
     <row r="50" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="1">
@@ -1917,7 +1910,7 @@
       <c r="E50" t="s">
         <v>14</v>
       </c>
-      <c r="I50" s="18"/>
+      <c r="I50" s="21"/>
     </row>
     <row r="51" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="1">
@@ -1932,7 +1925,7 @@
       <c r="E51" t="s">
         <v>14</v>
       </c>
-      <c r="I51" s="18"/>
+      <c r="I51" s="21"/>
     </row>
     <row r="52" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="2">
@@ -1947,7 +1940,7 @@
       <c r="E52" t="s">
         <v>14</v>
       </c>
-      <c r="I52" s="18"/>
+      <c r="I52" s="21"/>
     </row>
     <row r="53" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="2">
@@ -1962,7 +1955,7 @@
       <c r="E53" t="s">
         <v>14</v>
       </c>
-      <c r="I53" s="18"/>
+      <c r="I53" s="21"/>
     </row>
     <row r="54" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="3">
@@ -1980,7 +1973,7 @@
       <c r="E54" t="s">
         <v>14</v>
       </c>
-      <c r="I54" s="18"/>
+      <c r="I54" s="21"/>
     </row>
     <row r="55" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="3">
@@ -1995,7 +1988,7 @@
       <c r="E55" t="s">
         <v>14</v>
       </c>
-      <c r="I55" s="18"/>
+      <c r="I55" s="21"/>
     </row>
     <row r="56" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="3">
@@ -2010,7 +2003,7 @@
       <c r="E56" t="s">
         <v>14</v>
       </c>
-      <c r="I56" s="18"/>
+      <c r="I56" s="21"/>
     </row>
     <row r="57" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="3">
@@ -2025,7 +2018,7 @@
       <c r="E57" t="s">
         <v>14</v>
       </c>
-      <c r="I57" s="18"/>
+      <c r="I57" s="21"/>
     </row>
     <row r="58" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="3">
@@ -2040,7 +2033,7 @@
       <c r="E58" t="s">
         <v>14</v>
       </c>
-      <c r="I58" s="18"/>
+      <c r="I58" s="21"/>
     </row>
     <row r="59" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="3">
@@ -2055,25 +2048,22 @@
       <c r="E59" t="s">
         <v>14</v>
       </c>
-      <c r="I59" s="18"/>
+      <c r="I59" s="21"/>
     </row>
     <row r="60" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="3">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="C60" t="s">
-        <v>68</v>
+        <v>144</v>
       </c>
       <c r="D60" s="8">
         <v>59</v>
       </c>
       <c r="E60" t="s">
-        <v>14</v>
-      </c>
-      <c r="I60" s="18"/>
+        <v>6</v>
+      </c>
+      <c r="I60" s="21"/>
     </row>
     <row r="61" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="1">
@@ -2091,7 +2081,7 @@
       <c r="E61" t="s">
         <v>14</v>
       </c>
-      <c r="I61" s="18"/>
+      <c r="I61" s="21"/>
     </row>
     <row r="62" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="3">
@@ -2106,7 +2096,7 @@
       <c r="E62" t="s">
         <v>14</v>
       </c>
-      <c r="I62" s="18"/>
+      <c r="I62" s="21"/>
     </row>
     <row r="63" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="3">
@@ -2121,13 +2111,13 @@
       <c r="E63" t="s">
         <v>14</v>
       </c>
-      <c r="I63" s="18"/>
+      <c r="I63" s="21"/>
     </row>
     <row r="64" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="3">
         <v>34</v>
       </c>
-      <c r="B64" s="21" t="s">
+      <c r="B64" s="3" t="s">
         <v>145</v>
       </c>
       <c r="D64" s="8">
@@ -2136,7 +2126,7 @@
       <c r="E64" t="s">
         <v>6</v>
       </c>
-      <c r="I64" s="18"/>
+      <c r="I64" s="21"/>
     </row>
     <row r="65" spans="1:9" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="3">
@@ -2154,7 +2144,7 @@
       <c r="E65" t="s">
         <v>6</v>
       </c>
-      <c r="I65" s="18"/>
+      <c r="I65" s="21"/>
     </row>
     <row r="66" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="3">
@@ -2169,7 +2159,7 @@
       <c r="E66" t="s">
         <v>6</v>
       </c>
-      <c r="I66" s="18"/>
+      <c r="I66" s="21"/>
     </row>
     <row r="67" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="3">
@@ -2184,7 +2174,7 @@
       <c r="E67" t="s">
         <v>6</v>
       </c>
-      <c r="I67" s="18"/>
+      <c r="I67" s="21"/>
     </row>
     <row r="68" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="3">
@@ -2199,7 +2189,7 @@
       <c r="E68" t="s">
         <v>6</v>
       </c>
-      <c r="I68" s="18"/>
+      <c r="I68" s="21"/>
     </row>
     <row r="69" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="2">
@@ -2214,7 +2204,7 @@
       <c r="E69" t="s">
         <v>6</v>
       </c>
-      <c r="I69" s="18"/>
+      <c r="I69" s="21"/>
     </row>
     <row r="70" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="2">
@@ -2229,7 +2219,7 @@
       <c r="E70" t="s">
         <v>6</v>
       </c>
-      <c r="I70" s="18"/>
+      <c r="I70" s="21"/>
     </row>
     <row r="71" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A71" s="3">
@@ -2244,7 +2234,7 @@
       <c r="E71" t="s">
         <v>6</v>
       </c>
-      <c r="I71" s="18"/>
+      <c r="I71" s="21"/>
     </row>
     <row r="72" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="3">
@@ -2259,7 +2249,7 @@
       <c r="E72" t="s">
         <v>6</v>
       </c>
-      <c r="I72" s="18"/>
+      <c r="I72" s="21"/>
     </row>
     <row r="73" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="3">
@@ -2274,7 +2264,7 @@
       <c r="E73" t="s">
         <v>6</v>
       </c>
-      <c r="I73" s="18"/>
+      <c r="I73" s="21"/>
     </row>
     <row r="74" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="1">
@@ -2292,7 +2282,7 @@
       <c r="E74" t="s">
         <v>6</v>
       </c>
-      <c r="I74" s="18"/>
+      <c r="I74" s="21"/>
     </row>
     <row r="75" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="3">
@@ -2307,7 +2297,7 @@
       <c r="E75" t="s">
         <v>6</v>
       </c>
-      <c r="I75" s="18"/>
+      <c r="I75" s="21"/>
     </row>
     <row r="76" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="3">
@@ -2322,7 +2312,7 @@
       <c r="E76" t="s">
         <v>6</v>
       </c>
-      <c r="I76" s="18"/>
+      <c r="I76" s="21"/>
     </row>
     <row r="77" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="3">
@@ -2337,7 +2327,7 @@
       <c r="E77" t="s">
         <v>6</v>
       </c>
-      <c r="I77" s="18"/>
+      <c r="I77" s="21"/>
     </row>
     <row r="78" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="3">
@@ -2352,7 +2342,7 @@
       <c r="E78" t="s">
         <v>6</v>
       </c>
-      <c r="I78" s="18"/>
+      <c r="I78" s="21"/>
     </row>
     <row r="79" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="3">
@@ -2367,7 +2357,7 @@
       <c r="E79" t="s">
         <v>6</v>
       </c>
-      <c r="I79" s="18"/>
+      <c r="I79" s="21"/>
     </row>
     <row r="80" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="3">
@@ -2382,7 +2372,7 @@
       <c r="E80" t="s">
         <v>6</v>
       </c>
-      <c r="I80" s="18"/>
+      <c r="I80" s="21"/>
     </row>
     <row r="81" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" s="2">
@@ -2397,7 +2387,7 @@
       <c r="E81" t="s">
         <v>4</v>
       </c>
-      <c r="I81" s="18"/>
+      <c r="I81" s="21"/>
     </row>
     <row r="82" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" s="3">
@@ -2412,7 +2402,7 @@
       <c r="E82" t="s">
         <v>6</v>
       </c>
-      <c r="I82" s="18"/>
+      <c r="I82" s="21"/>
     </row>
     <row r="83" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A83" s="3">
@@ -2427,7 +2417,7 @@
       <c r="E83" t="s">
         <v>14</v>
       </c>
-      <c r="I83" s="18"/>
+      <c r="I83" s="21"/>
     </row>
     <row r="84" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84" s="3">
@@ -2442,7 +2432,7 @@
       <c r="E84" t="s">
         <v>14</v>
       </c>
-      <c r="I84" s="18"/>
+      <c r="I84" s="21"/>
     </row>
     <row r="85" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A85" s="3">
@@ -2460,13 +2450,13 @@
       <c r="E85" t="s">
         <v>14</v>
       </c>
-      <c r="I85" s="18"/>
+      <c r="I85" s="21"/>
     </row>
     <row r="86" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="3">
         <v>56</v>
       </c>
-      <c r="B86" s="21" t="s">
+      <c r="B86" s="3" t="s">
         <v>143</v>
       </c>
       <c r="D86" s="8">
@@ -2475,7 +2465,7 @@
       <c r="E86" t="s">
         <v>1</v>
       </c>
-      <c r="I86" s="18"/>
+      <c r="I86" s="21"/>
     </row>
     <row r="87" spans="1:9" s="4" customFormat="1" ht="13" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A87" s="6"/>
@@ -2490,7 +2480,7 @@
       <c r="F87" s="6"/>
       <c r="G87" s="6"/>
       <c r="H87" s="6"/>
-      <c r="I87" s="19"/>
+      <c r="I87" s="22"/>
     </row>
     <row r="88" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="3">
@@ -2505,7 +2495,7 @@
       <c r="E88" t="s">
         <v>6</v>
       </c>
-      <c r="I88" s="14" t="s">
+      <c r="I88" s="17" t="s">
         <v>133</v>
       </c>
     </row>
@@ -2522,14 +2512,14 @@
       <c r="E89" t="s">
         <v>6</v>
       </c>
-      <c r="I89" s="15"/>
+      <c r="I89" s="18"/>
     </row>
     <row r="90" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A90" s="3">
-        <v>50</v>
-      </c>
-      <c r="B90" s="22" t="s">
-        <v>144</v>
+      <c r="A90" s="1">
+        <v>24</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>5</v>
       </c>
       <c r="D90" s="8">
         <v>91</v>
@@ -2537,7 +2527,7 @@
       <c r="E90" t="s">
         <v>6</v>
       </c>
-      <c r="I90" s="15"/>
+      <c r="I90" s="18"/>
     </row>
     <row r="91" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A91" s="1">
@@ -2555,7 +2545,7 @@
       <c r="E91" t="s">
         <v>6</v>
       </c>
-      <c r="I91" s="15"/>
+      <c r="I91" s="18"/>
     </row>
     <row r="92" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A92" s="1">
@@ -2573,7 +2563,7 @@
       <c r="E92" t="s">
         <v>6</v>
       </c>
-      <c r="I92" s="15"/>
+      <c r="I92" s="18"/>
     </row>
     <row r="93" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A93" s="1">
@@ -2588,7 +2578,7 @@
       <c r="E93" t="s">
         <v>6</v>
       </c>
-      <c r="I93" s="15"/>
+      <c r="I93" s="18"/>
     </row>
     <row r="94" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A94" s="1">
@@ -2603,22 +2593,25 @@
       <c r="E94" t="s">
         <v>6</v>
       </c>
-      <c r="I94" s="15"/>
+      <c r="I94" s="18"/>
     </row>
     <row r="95" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A95" s="1">
-        <v>24</v>
-      </c>
-      <c r="B95" s="1" t="s">
-        <v>5</v>
+      <c r="A95" s="3">
+        <v>74</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C95" s="13" t="s">
+        <v>68</v>
       </c>
       <c r="D95" s="8">
         <v>96</v>
       </c>
       <c r="E95" t="s">
-        <v>6</v>
-      </c>
-      <c r="I95" s="15"/>
+        <v>14</v>
+      </c>
+      <c r="I95" s="18"/>
     </row>
     <row r="96" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A96" s="3">
@@ -2633,7 +2626,7 @@
       <c r="E96" t="s">
         <v>6</v>
       </c>
-      <c r="I96" s="15"/>
+      <c r="I96" s="18"/>
     </row>
     <row r="97" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A97" s="3">
@@ -2648,7 +2641,7 @@
       <c r="E97" t="s">
         <v>6</v>
       </c>
-      <c r="I97" s="15"/>
+      <c r="I97" s="18"/>
     </row>
     <row r="98" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A98" s="1">
@@ -2666,7 +2659,7 @@
       <c r="E98" t="s">
         <v>1</v>
       </c>
-      <c r="I98" s="15"/>
+      <c r="I98" s="18"/>
     </row>
     <row r="99" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A99" s="1">
@@ -2681,7 +2674,7 @@
       <c r="E99" t="s">
         <v>1</v>
       </c>
-      <c r="I99" s="15"/>
+      <c r="I99" s="18"/>
     </row>
     <row r="100" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A100" s="1">
@@ -2696,7 +2689,7 @@
       <c r="E100" t="s">
         <v>1</v>
       </c>
-      <c r="I100" s="15"/>
+      <c r="I100" s="18"/>
     </row>
     <row r="101" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A101" s="1">
@@ -2711,7 +2704,7 @@
       <c r="E101" t="s">
         <v>1</v>
       </c>
-      <c r="I101" s="15"/>
+      <c r="I101" s="18"/>
     </row>
     <row r="102" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A102" s="1">
@@ -2729,7 +2722,7 @@
       <c r="E102" t="s">
         <v>1</v>
       </c>
-      <c r="I102" s="15"/>
+      <c r="I102" s="18"/>
     </row>
     <row r="103" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A103" s="2">
@@ -2744,7 +2737,7 @@
       <c r="E103" t="s">
         <v>1</v>
       </c>
-      <c r="I103" s="15"/>
+      <c r="I103" s="18"/>
     </row>
     <row r="104" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A104" s="3">
@@ -2759,7 +2752,7 @@
       <c r="E104" t="s">
         <v>1</v>
       </c>
-      <c r="I104" s="15"/>
+      <c r="I104" s="18"/>
     </row>
     <row r="105" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A105" s="3">
@@ -2774,7 +2767,7 @@
       <c r="E105" t="s">
         <v>1</v>
       </c>
-      <c r="I105" s="15"/>
+      <c r="I105" s="18"/>
     </row>
     <row r="106" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A106" s="3">
@@ -2789,7 +2782,7 @@
       <c r="E106" t="s">
         <v>1</v>
       </c>
-      <c r="I106" s="15"/>
+      <c r="I106" s="18"/>
     </row>
     <row r="107" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A107" s="3">
@@ -2804,7 +2797,7 @@
       <c r="E107" t="s">
         <v>1</v>
       </c>
-      <c r="I107" s="15"/>
+      <c r="I107" s="18"/>
     </row>
     <row r="108" spans="1:9" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A108" s="1">
@@ -2819,7 +2812,7 @@
       <c r="E108" t="s">
         <v>1</v>
       </c>
-      <c r="I108" s="15"/>
+      <c r="I108" s="18"/>
     </row>
     <row r="109" spans="1:9" s="4" customFormat="1" ht="13" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A109" s="12">
@@ -2834,7 +2827,7 @@
       <c r="E109" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="I109" s="16"/>
+      <c r="I109" s="19"/>
     </row>
     <row r="110" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A110" s="1">
@@ -2849,7 +2842,7 @@
       <c r="E110" t="s">
         <v>1</v>
       </c>
-      <c r="I110" s="17" t="s">
+      <c r="I110" s="20" t="s">
         <v>135</v>
       </c>
     </row>
@@ -2866,7 +2859,7 @@
       <c r="E111" t="s">
         <v>1</v>
       </c>
-      <c r="I111" s="18"/>
+      <c r="I111" s="21"/>
     </row>
     <row r="112" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A112" s="2">
@@ -2881,7 +2874,7 @@
       <c r="E112" t="s">
         <v>1</v>
       </c>
-      <c r="I112" s="18"/>
+      <c r="I112" s="21"/>
     </row>
     <row r="113" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A113" s="3">
@@ -2896,7 +2889,7 @@
       <c r="E113" t="s">
         <v>1</v>
       </c>
-      <c r="I113" s="18"/>
+      <c r="I113" s="21"/>
     </row>
     <row r="114" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A114" s="3">
@@ -2911,7 +2904,7 @@
       <c r="E114" t="s">
         <v>1</v>
       </c>
-      <c r="I114" s="18"/>
+      <c r="I114" s="21"/>
     </row>
     <row r="115" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A115" s="3">
@@ -2926,7 +2919,7 @@
       <c r="E115" t="s">
         <v>1</v>
       </c>
-      <c r="I115" s="18"/>
+      <c r="I115" s="21"/>
     </row>
     <row r="116" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A116" s="1">
@@ -2941,7 +2934,7 @@
       <c r="E116" t="s">
         <v>1</v>
       </c>
-      <c r="I116" s="18"/>
+      <c r="I116" s="21"/>
     </row>
     <row r="117" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A117" s="1">
@@ -2956,7 +2949,7 @@
       <c r="E117" t="s">
         <v>1</v>
       </c>
-      <c r="I117" s="18"/>
+      <c r="I117" s="21"/>
     </row>
     <row r="118" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A118" s="1">
@@ -2971,7 +2964,7 @@
       <c r="E118" t="s">
         <v>1</v>
       </c>
-      <c r="I118" s="18"/>
+      <c r="I118" s="21"/>
     </row>
     <row r="119" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A119" s="1">
@@ -2986,7 +2979,7 @@
       <c r="E119" t="s">
         <v>1</v>
       </c>
-      <c r="I119" s="18"/>
+      <c r="I119" s="21"/>
     </row>
     <row r="120" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A120" s="1">
@@ -3004,7 +2997,7 @@
       <c r="E120" t="s">
         <v>1</v>
       </c>
-      <c r="I120" s="18"/>
+      <c r="I120" s="21"/>
     </row>
     <row r="121" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A121" s="1">
@@ -3019,7 +3012,7 @@
       <c r="E121" t="s">
         <v>1</v>
       </c>
-      <c r="I121" s="18"/>
+      <c r="I121" s="21"/>
     </row>
     <row r="122" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A122" s="1">
@@ -3034,7 +3027,7 @@
       <c r="E122" t="s">
         <v>1</v>
       </c>
-      <c r="I122" s="18"/>
+      <c r="I122" s="21"/>
     </row>
     <row r="123" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A123" s="1">
@@ -3049,7 +3042,7 @@
       <c r="E123" t="s">
         <v>1</v>
       </c>
-      <c r="I123" s="18"/>
+      <c r="I123" s="21"/>
     </row>
     <row r="124" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A124" s="1">
@@ -3067,7 +3060,7 @@
       <c r="E124" t="s">
         <v>1</v>
       </c>
-      <c r="I124" s="18"/>
+      <c r="I124" s="21"/>
     </row>
     <row r="125" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A125" s="1">
@@ -3082,7 +3075,7 @@
       <c r="E125" t="s">
         <v>1</v>
       </c>
-      <c r="I125" s="18"/>
+      <c r="I125" s="21"/>
     </row>
     <row r="126" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A126" s="2">
@@ -3097,7 +3090,7 @@
       <c r="E126" t="s">
         <v>1</v>
       </c>
-      <c r="I126" s="18"/>
+      <c r="I126" s="21"/>
     </row>
     <row r="127" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A127" s="3">
@@ -3112,7 +3105,7 @@
       <c r="E127" t="s">
         <v>1</v>
       </c>
-      <c r="I127" s="18"/>
+      <c r="I127" s="21"/>
     </row>
     <row r="128" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A128" s="3">
@@ -3127,7 +3120,7 @@
       <c r="E128" t="s">
         <v>1</v>
       </c>
-      <c r="I128" s="18"/>
+      <c r="I128" s="21"/>
     </row>
     <row r="129" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A129" s="3">
@@ -3145,7 +3138,7 @@
       <c r="E129" t="s">
         <v>1</v>
       </c>
-      <c r="I129" s="18"/>
+      <c r="I129" s="21"/>
     </row>
     <row r="130" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A130" s="2">
@@ -3160,13 +3153,13 @@
       <c r="E130" t="s">
         <v>1</v>
       </c>
-      <c r="I130" s="18"/>
+      <c r="I130" s="21"/>
     </row>
     <row r="131" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A131" s="3">
         <v>6</v>
       </c>
-      <c r="B131" s="21" t="s">
+      <c r="B131" s="3" t="s">
         <v>141</v>
       </c>
       <c r="C131" s="13" t="s">
@@ -3178,13 +3171,13 @@
       <c r="E131" t="s">
         <v>1</v>
       </c>
-      <c r="I131" s="18"/>
+      <c r="I131" s="21"/>
     </row>
     <row r="132" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A132" s="3">
         <v>43</v>
       </c>
-      <c r="B132" s="21" t="s">
+      <c r="B132" s="3" t="s">
         <v>142</v>
       </c>
       <c r="D132" s="8">
@@ -3193,7 +3186,7 @@
       <c r="E132" t="s">
         <v>1</v>
       </c>
-      <c r="I132" s="18"/>
+      <c r="I132" s="21"/>
     </row>
     <row r="133" spans="1:9" s="4" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A133" s="6"/>
@@ -3208,7 +3201,7 @@
       <c r="F133" s="6"/>
       <c r="G133" s="6"/>
       <c r="H133" s="6"/>
-      <c r="I133" s="19"/>
+      <c r="I133" s="22"/>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A135" s="1"/>

--- a/STAIX2026/assets/Poster-Presentation-Label-Assignment.xlsx
+++ b/STAIX2026/assets/Poster-Presentation-Label-Assignment.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tracyke/Dropbox/Mac (2)/Documents/2026/STAI-X conference/Poster session/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E07E6659-BFEC-D046-878E-7CCBF2DA6420}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B4F0BE9-0B4A-F04B-9B83-2CBD0C7B3A8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="500" windowWidth="38400" windowHeight="19240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10580" yWindow="500" windowWidth="38400" windowHeight="19240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Assignment" sheetId="7" r:id="rId1"/>
@@ -140,9 +140,6 @@
     <t>Bridging Probabilistic LLMs and Deterministic Statistical Validation: The PROVE Multi-Agent Framework for Clinical Trial Reporting</t>
   </si>
   <si>
-    <t>Transformers as Provable Approximators of Sparse Principal Component Analysis</t>
-  </si>
-  <si>
     <t>Matching Rates and Optimal Allocation for Federated Probe-Logit Distillation under Heterogeneous Bandwidth Budgets</t>
   </si>
   <si>
@@ -455,9 +452,6 @@
     <t>Paper Honorable</t>
   </si>
   <si>
-    <t>prediction-only distillation with optimal mixing in ridge-regularized linear and logistic regression</t>
-  </si>
-  <si>
     <t>Vertical Consensus Inference for High-Dimensional Random Partition</t>
   </si>
   <si>
@@ -480,6 +474,12 @@
   </si>
   <si>
     <t>86-88</t>
+  </si>
+  <si>
+    <t>Bridging Data Gaps in Oncology: Integrating Large Language Models and Recommendation Systems for Evidence Synthesis</t>
+  </si>
+  <si>
+    <t>Latent-Factor Score Normalization for Conformal Prediction on Multi-resolution Mobile Health Data</t>
   </si>
 </sst>
 </file>
@@ -600,7 +600,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
@@ -638,6 +638,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1139,19 +1140,19 @@
   <sheetData>
     <row r="1" spans="1:9" s="4" customFormat="1" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A1" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="C1" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="D1" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="E1" s="11" t="s">
         <v>129</v>
-      </c>
-      <c r="E1" s="11" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
@@ -1168,7 +1169,7 @@
         <v>4</v>
       </c>
       <c r="I2" s="17" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.15">
@@ -1209,7 +1210,7 @@
         <v>22</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D5" s="8">
         <v>4</v>
@@ -1224,7 +1225,7 @@
         <v>28</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D6" s="8">
         <v>5</v>
@@ -1239,7 +1240,7 @@
         <v>11</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D7" s="8">
         <v>6</v>
@@ -1254,7 +1255,7 @@
         <v>15</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D8" s="8">
         <v>7</v>
@@ -1269,7 +1270,7 @@
         <v>39</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D9" s="8">
         <v>8</v>
@@ -1284,7 +1285,7 @@
         <v>58</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D10" s="8">
         <v>9</v>
@@ -1299,7 +1300,7 @@
         <v>119</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D11" s="8">
         <v>10</v>
@@ -1314,10 +1315,10 @@
         <v>130</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D12" s="8">
         <v>11</v>
@@ -1332,7 +1333,7 @@
         <v>63</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D13" s="8">
         <v>12</v>
@@ -1347,7 +1348,7 @@
         <v>64</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D14" s="8">
         <v>13</v>
@@ -1362,7 +1363,7 @@
         <v>68</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D15" s="8">
         <v>14</v>
@@ -1377,7 +1378,7 @@
         <v>71</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D16" s="8">
         <v>15</v>
@@ -1392,7 +1393,7 @@
         <v>75</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D17" s="8">
         <v>16</v>
@@ -1452,7 +1453,7 @@
         <v>35</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D21" s="8">
         <v>20</v>
@@ -1467,7 +1468,7 @@
         <v>1</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D22" s="8">
         <v>21</v>
@@ -1482,7 +1483,7 @@
         <v>2</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D23" s="8">
         <v>22</v>
@@ -1497,7 +1498,7 @@
         <v>19</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D24" s="8">
         <v>23</v>
@@ -1512,10 +1513,10 @@
         <v>35</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C25" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D25" s="8">
         <v>24</v>
@@ -1530,7 +1531,7 @@
         <v>106</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D26" s="8">
         <v>25</v>
@@ -1563,7 +1564,7 @@
         <v>129</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D28" s="8">
         <v>27</v>
@@ -1578,10 +1579,10 @@
         <v>38</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C29" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D29" s="8">
         <v>28</v>
@@ -1596,7 +1597,7 @@
         <v>67</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D30" s="8">
         <v>29</v>
@@ -1611,7 +1612,7 @@
         <v>77</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D31" s="8">
         <v>30</v>
@@ -1626,7 +1627,7 @@
         <v>78</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D32" s="8">
         <v>31</v>
@@ -1641,7 +1642,7 @@
         <v>129</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D33" s="8">
         <v>32</v>
@@ -1656,7 +1657,7 @@
         <v>22</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D34" s="8">
         <v>33</v>
@@ -1719,7 +1720,7 @@
         <v>26</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D38" s="8">
         <v>37</v>
@@ -1734,7 +1735,7 @@
         <v>46</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D39" s="8">
         <v>38</v>
@@ -1749,10 +1750,10 @@
         <v>3</v>
       </c>
       <c r="B40" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C40" t="s">
         <v>67</v>
-      </c>
-      <c r="C40" t="s">
-        <v>68</v>
       </c>
       <c r="D40" s="8">
         <v>39</v>
@@ -1767,7 +1768,7 @@
         <v>10</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D41" s="8">
         <v>40</v>
@@ -1782,7 +1783,7 @@
         <v>14</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D42" s="8">
         <v>41</v>
@@ -1797,7 +1798,7 @@
         <v>32</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D43" s="8">
         <v>42</v>
@@ -1812,7 +1813,7 @@
         <v>37</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D44" s="8">
         <v>43</v>
@@ -1840,7 +1841,7 @@
         <v>40</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D46" s="8">
         <v>45</v>
@@ -1849,7 +1850,7 @@
         <v>14</v>
       </c>
       <c r="I46" s="20" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
@@ -1857,7 +1858,7 @@
         <v>45</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D47" s="8">
         <v>46</v>
@@ -1884,15 +1885,15 @@
     </row>
     <row r="49" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="1">
-        <v>63</v>
+        <v>32</v>
       </c>
       <c r="B49" s="14" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="D49" s="8">
         <v>48</v>
       </c>
-      <c r="E49" t="s">
+      <c r="E49" s="13" t="s">
         <v>14</v>
       </c>
       <c r="I49" s="21"/>
@@ -1932,7 +1933,7 @@
         <v>75</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D52" s="8">
         <v>51</v>
@@ -1947,7 +1948,7 @@
         <v>96</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D53" s="8">
         <v>52</v>
@@ -1962,10 +1963,10 @@
         <v>48</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C54" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D54" s="8">
         <v>53</v>
@@ -1980,7 +1981,7 @@
         <v>49</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D55" s="8">
         <v>54</v>
@@ -1995,7 +1996,7 @@
         <v>55</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D56" s="8">
         <v>55</v>
@@ -2010,7 +2011,7 @@
         <v>59</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D57" s="8">
         <v>56</v>
@@ -2025,7 +2026,7 @@
         <v>66</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D58" s="8">
         <v>57</v>
@@ -2040,7 +2041,7 @@
         <v>70</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D59" s="8">
         <v>58</v>
@@ -2055,7 +2056,7 @@
         <v>50</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D60" s="8">
         <v>59</v>
@@ -2070,7 +2071,7 @@
         <v>143</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C61" t="s">
         <v>13</v>
@@ -2088,7 +2089,7 @@
         <v>83</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D62" s="8">
         <v>61</v>
@@ -2103,7 +2104,7 @@
         <v>87</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D63" s="8">
         <v>62</v>
@@ -2118,7 +2119,7 @@
         <v>34</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D64" s="8">
         <v>63</v>
@@ -2133,10 +2134,10 @@
         <v>47</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C65" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D65" s="8">
         <v>64</v>
@@ -2151,7 +2152,7 @@
         <v>54</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D66" s="8">
         <v>65</v>
@@ -2166,7 +2167,7 @@
         <v>60</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D67" s="8">
         <v>66</v>
@@ -2181,7 +2182,7 @@
         <v>65</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D68" s="8">
         <v>67</v>
@@ -2196,7 +2197,7 @@
         <v>103</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D69" s="8">
         <v>68</v>
@@ -2211,7 +2212,7 @@
         <v>111</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D70" s="8">
         <v>69</v>
@@ -2226,7 +2227,7 @@
         <v>65</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D71" s="8">
         <v>70</v>
@@ -2241,7 +2242,7 @@
         <v>79</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D72" s="8">
         <v>71</v>
@@ -2256,7 +2257,7 @@
         <v>81</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D73" s="8">
         <v>72</v>
@@ -2274,7 +2275,7 @@
         <v>34</v>
       </c>
       <c r="C74" s="13" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D74" s="8">
         <v>73</v>
@@ -2289,7 +2290,7 @@
         <v>53</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D75" s="8">
         <v>74</v>
@@ -2304,7 +2305,7 @@
         <v>7</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D76" s="8">
         <v>75</v>
@@ -2319,7 +2320,7 @@
         <v>8</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D77" s="8">
         <v>76</v>
@@ -2334,7 +2335,7 @@
         <v>24</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D78" s="8">
         <v>77</v>
@@ -2349,7 +2350,7 @@
         <v>20</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D79" s="8">
         <v>78</v>
@@ -2364,7 +2365,7 @@
         <v>24</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D80" s="8">
         <v>79</v>
@@ -2379,7 +2380,7 @@
         <v>136</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D81" s="8">
         <v>80</v>
@@ -2394,7 +2395,7 @@
         <v>72</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D82" s="8">
         <v>81</v>
@@ -2409,7 +2410,7 @@
         <v>82</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D83" s="8">
         <v>82</v>
@@ -2424,7 +2425,7 @@
         <v>80</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D84" s="8">
         <v>83</v>
@@ -2439,10 +2440,10 @@
         <v>61</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C85" s="13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D85" s="8">
         <v>84</v>
@@ -2457,7 +2458,7 @@
         <v>56</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D86" s="8">
         <v>85</v>
@@ -2470,11 +2471,11 @@
     <row r="87" spans="1:9" s="4" customFormat="1" ht="13" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A87" s="6"/>
       <c r="B87" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C87" s="6"/>
       <c r="D87" s="9" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E87" s="6"/>
       <c r="F87" s="6"/>
@@ -2487,7 +2488,7 @@
         <v>31</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D88" s="8">
         <v>89</v>
@@ -2496,7 +2497,7 @@
         <v>6</v>
       </c>
       <c r="I88" s="17" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="89" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
@@ -2504,7 +2505,7 @@
         <v>58</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D89" s="8">
         <v>90</v>
@@ -2534,7 +2535,7 @@
         <v>122</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C91" t="s">
         <v>13</v>
@@ -2552,7 +2553,7 @@
         <v>132</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C92" t="s">
         <v>13</v>
@@ -2600,10 +2601,10 @@
         <v>74</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C95" s="13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D95" s="8">
         <v>96</v>
@@ -2618,7 +2619,7 @@
         <v>44</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D96" s="8">
         <v>97</v>
@@ -2633,7 +2634,7 @@
         <v>46</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D97" s="8">
         <v>98</v>
@@ -2648,7 +2649,7 @@
         <v>137</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C98" t="s">
         <v>13</v>
@@ -2666,7 +2667,7 @@
         <v>139</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D99" s="8">
         <v>100</v>
@@ -2681,7 +2682,7 @@
         <v>141</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D100" s="8">
         <v>101</v>
@@ -2729,7 +2730,7 @@
         <v>47</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D103" s="8">
         <v>103</v>
@@ -2744,7 +2745,7 @@
         <v>17</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D104" s="8">
         <v>105</v>
@@ -2759,7 +2760,7 @@
         <v>18</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D105" s="8">
         <v>106</v>
@@ -2774,7 +2775,7 @@
         <v>21</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D106" s="8">
         <v>107</v>
@@ -2789,7 +2790,7 @@
         <v>23</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D107" s="8">
         <v>108</v>
@@ -2843,7 +2844,7 @@
         <v>1</v>
       </c>
       <c r="I110" s="20" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="111" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
@@ -2866,7 +2867,7 @@
         <v>47</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D112" s="8">
         <v>113</v>
@@ -2881,7 +2882,7 @@
         <v>29</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D113" s="8">
         <v>114</v>
@@ -2896,7 +2897,7 @@
         <v>30</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D114" s="8">
         <v>115</v>
@@ -2911,7 +2912,7 @@
         <v>36</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D115" s="8">
         <v>116</v>
@@ -3015,17 +3016,17 @@
       <c r="I121" s="21"/>
     </row>
     <row r="122" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A122" s="1">
-        <v>116</v>
-      </c>
-      <c r="B122" s="1" t="s">
-        <v>35</v>
+      <c r="A122" s="3">
+        <v>69</v>
+      </c>
+      <c r="B122" s="23" t="s">
+        <v>148</v>
       </c>
       <c r="D122" s="8">
         <v>123</v>
       </c>
-      <c r="E122" t="s">
-        <v>1</v>
+      <c r="E122" s="13" t="s">
+        <v>14</v>
       </c>
       <c r="I122" s="21"/>
     </row>
@@ -3034,7 +3035,7 @@
         <v>117</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D123" s="8">
         <v>124</v>
@@ -3049,10 +3050,10 @@
         <v>124</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C124" s="13" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D124" s="8">
         <v>125</v>
@@ -3067,7 +3068,7 @@
         <v>128</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D125" s="8">
         <v>126</v>
@@ -3082,7 +3083,7 @@
         <v>102</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D126" s="8">
         <v>127</v>
@@ -3097,7 +3098,7 @@
         <v>42</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D127" s="8">
         <v>128</v>
@@ -3112,7 +3113,7 @@
         <v>52</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D128" s="8">
         <v>129</v>
@@ -3127,10 +3128,10 @@
         <v>86</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C129" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D129" s="8">
         <v>130</v>
@@ -3145,7 +3146,7 @@
         <v>135</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D130" s="8">
         <v>131</v>
@@ -3160,10 +3161,10 @@
         <v>6</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C131" s="13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D131" s="8">
         <v>132</v>
@@ -3178,7 +3179,7 @@
         <v>43</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D132" s="8">
         <v>133</v>
@@ -3191,7 +3192,7 @@
     <row r="133" spans="1:9" s="4" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A133" s="6"/>
       <c r="B133" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C133" s="6"/>
       <c r="D133" s="9">
@@ -3206,19 +3207,19 @@
     <row r="135" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A135" s="1"/>
       <c r="B135" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A136" s="2"/>
       <c r="B136" s="10" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A137" s="3"/>
       <c r="B137" s="10" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>

--- a/STAIX2026/assets/Poster-Presentation-Label-Assignment.xlsx
+++ b/STAIX2026/assets/Poster-Presentation-Label-Assignment.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tracyke/Dropbox/Mac (2)/Documents/2026/STAI-X conference/Poster session/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B4F0BE9-0B4A-F04B-9B83-2CBD0C7B3A8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DC0A504-326B-7043-8FEF-48FC2A381FCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10580" yWindow="500" windowWidth="38400" windowHeight="19240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Assignment" sheetId="7" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="150">
   <si>
     <t>Design-Based Supervised Learning with Noisy Human Labels</t>
   </si>
@@ -480,6 +480,9 @@
   </si>
   <si>
     <t>Latent-Factor Score Normalization for Conformal Prediction on Multi-resolution Mobile Health Data</t>
+  </si>
+  <si>
+    <t>The ATLAS Penalty: Auxiliary-Transformed Location-Aware Smoothing with Applications to Spatial Transcriptomics</t>
   </si>
 </sst>
 </file>
@@ -600,7 +603,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
@@ -620,6 +623,7 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -638,7 +642,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1168,7 +1172,7 @@
       <c r="E2" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="17" t="s">
+      <c r="I2" s="18" t="s">
         <v>130</v>
       </c>
     </row>
@@ -1185,7 +1189,7 @@
       <c r="E3" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="18"/>
+      <c r="I3" s="19"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A4" s="1">
@@ -1203,7 +1207,7 @@
       <c r="E4" t="s">
         <v>4</v>
       </c>
-      <c r="I4" s="18"/>
+      <c r="I4" s="19"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A5" s="2">
@@ -1218,7 +1222,7 @@
       <c r="E5" t="s">
         <v>4</v>
       </c>
-      <c r="I5" s="18"/>
+      <c r="I5" s="19"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A6" s="2">
@@ -1233,7 +1237,7 @@
       <c r="E6" t="s">
         <v>4</v>
       </c>
-      <c r="I6" s="18"/>
+      <c r="I6" s="19"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A7" s="3">
@@ -1248,7 +1252,7 @@
       <c r="E7" t="s">
         <v>4</v>
       </c>
-      <c r="I7" s="18"/>
+      <c r="I7" s="19"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A8" s="3">
@@ -1263,7 +1267,7 @@
       <c r="E8" t="s">
         <v>4</v>
       </c>
-      <c r="I8" s="18"/>
+      <c r="I8" s="19"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A9" s="3">
@@ -1278,7 +1282,7 @@
       <c r="E9" t="s">
         <v>4</v>
       </c>
-      <c r="I9" s="18"/>
+      <c r="I9" s="19"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A10" s="3">
@@ -1293,7 +1297,7 @@
       <c r="E10" t="s">
         <v>4</v>
       </c>
-      <c r="I10" s="18"/>
+      <c r="I10" s="19"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A11" s="1">
@@ -1308,7 +1312,7 @@
       <c r="E11" t="s">
         <v>4</v>
       </c>
-      <c r="I11" s="18"/>
+      <c r="I11" s="19"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A12" s="1">
@@ -1326,7 +1330,7 @@
       <c r="E12" t="s">
         <v>4</v>
       </c>
-      <c r="I12" s="18"/>
+      <c r="I12" s="19"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A13" s="3">
@@ -1341,7 +1345,7 @@
       <c r="E13" t="s">
         <v>4</v>
       </c>
-      <c r="I13" s="18"/>
+      <c r="I13" s="19"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A14" s="3">
@@ -1356,7 +1360,7 @@
       <c r="E14" t="s">
         <v>4</v>
       </c>
-      <c r="I14" s="18"/>
+      <c r="I14" s="19"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A15" s="3">
@@ -1371,7 +1375,7 @@
       <c r="E15" t="s">
         <v>4</v>
       </c>
-      <c r="I15" s="18"/>
+      <c r="I15" s="19"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A16" s="3">
@@ -1386,7 +1390,7 @@
       <c r="E16" t="s">
         <v>4</v>
       </c>
-      <c r="I16" s="18"/>
+      <c r="I16" s="19"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A17" s="3">
@@ -1401,7 +1405,7 @@
       <c r="E17" t="s">
         <v>4</v>
       </c>
-      <c r="I17" s="18"/>
+      <c r="I17" s="19"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A18" s="1">
@@ -1416,7 +1420,7 @@
       <c r="E18" t="s">
         <v>8</v>
       </c>
-      <c r="I18" s="18"/>
+      <c r="I18" s="19"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A19" s="1">
@@ -1431,7 +1435,7 @@
       <c r="E19" t="s">
         <v>8</v>
       </c>
-      <c r="I19" s="18"/>
+      <c r="I19" s="19"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A20" s="1">
@@ -1446,7 +1450,7 @@
       <c r="E20" t="s">
         <v>8</v>
       </c>
-      <c r="I20" s="18"/>
+      <c r="I20" s="19"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A21" s="2">
@@ -1461,7 +1465,7 @@
       <c r="E21" t="s">
         <v>8</v>
       </c>
-      <c r="I21" s="18"/>
+      <c r="I21" s="19"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A22" s="3">
@@ -1476,7 +1480,7 @@
       <c r="E22" t="s">
         <v>8</v>
       </c>
-      <c r="I22" s="18"/>
+      <c r="I22" s="19"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A23" s="3">
@@ -1491,7 +1495,7 @@
       <c r="E23" t="s">
         <v>8</v>
       </c>
-      <c r="I23" s="18"/>
+      <c r="I23" s="19"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A24" s="3">
@@ -1506,7 +1510,7 @@
       <c r="E24" t="s">
         <v>8</v>
       </c>
-      <c r="I24" s="18"/>
+      <c r="I24" s="19"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A25" s="3">
@@ -1524,7 +1528,7 @@
       <c r="E25" t="s">
         <v>8</v>
       </c>
-      <c r="I25" s="18"/>
+      <c r="I25" s="19"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A26" s="2">
@@ -1539,7 +1543,7 @@
       <c r="E26" t="s">
         <v>8</v>
       </c>
-      <c r="I26" s="18"/>
+      <c r="I26" s="19"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A27" s="1">
@@ -1557,7 +1561,7 @@
       <c r="E27" t="s">
         <v>8</v>
       </c>
-      <c r="I27" s="18"/>
+      <c r="I27" s="19"/>
     </row>
     <row r="28" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="1">
@@ -1572,7 +1576,7 @@
       <c r="E28" t="s">
         <v>8</v>
       </c>
-      <c r="I28" s="18"/>
+      <c r="I28" s="19"/>
     </row>
     <row r="29" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="3">
@@ -1590,7 +1594,7 @@
       <c r="E29" t="s">
         <v>8</v>
       </c>
-      <c r="I29" s="18"/>
+      <c r="I29" s="19"/>
     </row>
     <row r="30" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="3">
@@ -1605,7 +1609,7 @@
       <c r="E30" t="s">
         <v>8</v>
       </c>
-      <c r="I30" s="18"/>
+      <c r="I30" s="19"/>
     </row>
     <row r="31" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="3">
@@ -1620,7 +1624,7 @@
       <c r="E31" t="s">
         <v>8</v>
       </c>
-      <c r="I31" s="18"/>
+      <c r="I31" s="19"/>
     </row>
     <row r="32" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="3">
@@ -1635,7 +1639,7 @@
       <c r="E32" t="s">
         <v>8</v>
       </c>
-      <c r="I32" s="18"/>
+      <c r="I32" s="19"/>
     </row>
     <row r="33" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="2">
@@ -1650,7 +1654,7 @@
       <c r="E33" t="s">
         <v>8</v>
       </c>
-      <c r="I33" s="18"/>
+      <c r="I33" s="19"/>
     </row>
     <row r="34" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="3">
@@ -1665,25 +1669,22 @@
       <c r="E34" t="s">
         <v>14</v>
       </c>
-      <c r="I34" s="18"/>
+      <c r="I34" s="19"/>
     </row>
     <row r="35" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="1">
-        <v>44</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C35" t="s">
-        <v>13</v>
+        <v>115</v>
+      </c>
+      <c r="B35" s="24" t="s">
+        <v>149</v>
       </c>
       <c r="D35" s="8">
         <v>34</v>
       </c>
-      <c r="E35" t="s">
-        <v>14</v>
-      </c>
-      <c r="I35" s="18"/>
+      <c r="E35" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="I35" s="19"/>
     </row>
     <row r="36" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="1">
@@ -1698,7 +1699,7 @@
       <c r="E36" t="s">
         <v>14</v>
       </c>
-      <c r="I36" s="18"/>
+      <c r="I36" s="19"/>
     </row>
     <row r="37" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="1">
@@ -1713,7 +1714,7 @@
       <c r="E37" t="s">
         <v>14</v>
       </c>
-      <c r="I37" s="18"/>
+      <c r="I37" s="19"/>
     </row>
     <row r="38" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="2">
@@ -1728,7 +1729,7 @@
       <c r="E38" t="s">
         <v>14</v>
       </c>
-      <c r="I38" s="18"/>
+      <c r="I38" s="19"/>
     </row>
     <row r="39" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="2">
@@ -1743,7 +1744,7 @@
       <c r="E39" t="s">
         <v>14</v>
       </c>
-      <c r="I39" s="18"/>
+      <c r="I39" s="19"/>
     </row>
     <row r="40" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="3">
@@ -1761,7 +1762,7 @@
       <c r="E40" t="s">
         <v>14</v>
       </c>
-      <c r="I40" s="18"/>
+      <c r="I40" s="19"/>
     </row>
     <row r="41" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="3">
@@ -1776,7 +1777,7 @@
       <c r="E41" t="s">
         <v>14</v>
       </c>
-      <c r="I41" s="18"/>
+      <c r="I41" s="19"/>
     </row>
     <row r="42" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="3">
@@ -1791,7 +1792,7 @@
       <c r="E42" t="s">
         <v>14</v>
       </c>
-      <c r="I42" s="18"/>
+      <c r="I42" s="19"/>
     </row>
     <row r="43" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="3">
@@ -1806,7 +1807,7 @@
       <c r="E43" t="s">
         <v>14</v>
       </c>
-      <c r="I43" s="18"/>
+      <c r="I43" s="19"/>
     </row>
     <row r="44" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="3">
@@ -1821,7 +1822,7 @@
       <c r="E44" t="s">
         <v>14</v>
       </c>
-      <c r="I44" s="18"/>
+      <c r="I44" s="19"/>
     </row>
     <row r="45" spans="1:9" s="4" customFormat="1" ht="13" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A45" s="15"/>
@@ -1834,7 +1835,7 @@
       <c r="F45" s="15"/>
       <c r="G45" s="15"/>
       <c r="H45" s="15"/>
-      <c r="I45" s="19"/>
+      <c r="I45" s="20"/>
     </row>
     <row r="46" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="3">
@@ -1849,7 +1850,7 @@
       <c r="E46" t="s">
         <v>14</v>
       </c>
-      <c r="I46" s="20" t="s">
+      <c r="I46" s="21" t="s">
         <v>131</v>
       </c>
     </row>
@@ -1866,7 +1867,7 @@
       <c r="E47" t="s">
         <v>14</v>
       </c>
-      <c r="I47" s="21"/>
+      <c r="I47" s="22"/>
     </row>
     <row r="48" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="1">
@@ -1881,7 +1882,7 @@
       <c r="E48" t="s">
         <v>14</v>
       </c>
-      <c r="I48" s="21"/>
+      <c r="I48" s="22"/>
     </row>
     <row r="49" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="1">
@@ -1896,7 +1897,7 @@
       <c r="E49" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="I49" s="21"/>
+      <c r="I49" s="22"/>
     </row>
     <row r="50" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="1">
@@ -1911,7 +1912,7 @@
       <c r="E50" t="s">
         <v>14</v>
       </c>
-      <c r="I50" s="21"/>
+      <c r="I50" s="22"/>
     </row>
     <row r="51" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="1">
@@ -1926,7 +1927,7 @@
       <c r="E51" t="s">
         <v>14</v>
       </c>
-      <c r="I51" s="21"/>
+      <c r="I51" s="22"/>
     </row>
     <row r="52" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="2">
@@ -1941,7 +1942,7 @@
       <c r="E52" t="s">
         <v>14</v>
       </c>
-      <c r="I52" s="21"/>
+      <c r="I52" s="22"/>
     </row>
     <row r="53" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="2">
@@ -1956,7 +1957,7 @@
       <c r="E53" t="s">
         <v>14</v>
       </c>
-      <c r="I53" s="21"/>
+      <c r="I53" s="22"/>
     </row>
     <row r="54" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="3">
@@ -1974,7 +1975,7 @@
       <c r="E54" t="s">
         <v>14</v>
       </c>
-      <c r="I54" s="21"/>
+      <c r="I54" s="22"/>
     </row>
     <row r="55" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="3">
@@ -1989,7 +1990,7 @@
       <c r="E55" t="s">
         <v>14</v>
       </c>
-      <c r="I55" s="21"/>
+      <c r="I55" s="22"/>
     </row>
     <row r="56" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="3">
@@ -2004,7 +2005,7 @@
       <c r="E56" t="s">
         <v>14</v>
       </c>
-      <c r="I56" s="21"/>
+      <c r="I56" s="22"/>
     </row>
     <row r="57" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="3">
@@ -2019,7 +2020,7 @@
       <c r="E57" t="s">
         <v>14</v>
       </c>
-      <c r="I57" s="21"/>
+      <c r="I57" s="22"/>
     </row>
     <row r="58" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="3">
@@ -2034,7 +2035,7 @@
       <c r="E58" t="s">
         <v>14</v>
       </c>
-      <c r="I58" s="21"/>
+      <c r="I58" s="22"/>
     </row>
     <row r="59" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="3">
@@ -2049,7 +2050,7 @@
       <c r="E59" t="s">
         <v>14</v>
       </c>
-      <c r="I59" s="21"/>
+      <c r="I59" s="22"/>
     </row>
     <row r="60" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="3">
@@ -2064,7 +2065,7 @@
       <c r="E60" t="s">
         <v>6</v>
       </c>
-      <c r="I60" s="21"/>
+      <c r="I60" s="22"/>
     </row>
     <row r="61" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="1">
@@ -2082,7 +2083,7 @@
       <c r="E61" t="s">
         <v>14</v>
       </c>
-      <c r="I61" s="21"/>
+      <c r="I61" s="22"/>
     </row>
     <row r="62" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="3">
@@ -2097,7 +2098,7 @@
       <c r="E62" t="s">
         <v>14</v>
       </c>
-      <c r="I62" s="21"/>
+      <c r="I62" s="22"/>
     </row>
     <row r="63" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="3">
@@ -2112,7 +2113,7 @@
       <c r="E63" t="s">
         <v>14</v>
       </c>
-      <c r="I63" s="21"/>
+      <c r="I63" s="22"/>
     </row>
     <row r="64" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="3">
@@ -2127,7 +2128,7 @@
       <c r="E64" t="s">
         <v>6</v>
       </c>
-      <c r="I64" s="21"/>
+      <c r="I64" s="22"/>
     </row>
     <row r="65" spans="1:9" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="3">
@@ -2145,7 +2146,7 @@
       <c r="E65" t="s">
         <v>6</v>
       </c>
-      <c r="I65" s="21"/>
+      <c r="I65" s="22"/>
     </row>
     <row r="66" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="3">
@@ -2160,7 +2161,7 @@
       <c r="E66" t="s">
         <v>6</v>
       </c>
-      <c r="I66" s="21"/>
+      <c r="I66" s="22"/>
     </row>
     <row r="67" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="3">
@@ -2175,7 +2176,7 @@
       <c r="E67" t="s">
         <v>6</v>
       </c>
-      <c r="I67" s="21"/>
+      <c r="I67" s="22"/>
     </row>
     <row r="68" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="3">
@@ -2190,7 +2191,7 @@
       <c r="E68" t="s">
         <v>6</v>
       </c>
-      <c r="I68" s="21"/>
+      <c r="I68" s="22"/>
     </row>
     <row r="69" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="2">
@@ -2205,7 +2206,7 @@
       <c r="E69" t="s">
         <v>6</v>
       </c>
-      <c r="I69" s="21"/>
+      <c r="I69" s="22"/>
     </row>
     <row r="70" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="2">
@@ -2220,7 +2221,7 @@
       <c r="E70" t="s">
         <v>6</v>
       </c>
-      <c r="I70" s="21"/>
+      <c r="I70" s="22"/>
     </row>
     <row r="71" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A71" s="3">
@@ -2235,7 +2236,7 @@
       <c r="E71" t="s">
         <v>6</v>
       </c>
-      <c r="I71" s="21"/>
+      <c r="I71" s="22"/>
     </row>
     <row r="72" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="3">
@@ -2250,7 +2251,7 @@
       <c r="E72" t="s">
         <v>6</v>
       </c>
-      <c r="I72" s="21"/>
+      <c r="I72" s="22"/>
     </row>
     <row r="73" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="3">
@@ -2265,7 +2266,7 @@
       <c r="E73" t="s">
         <v>6</v>
       </c>
-      <c r="I73" s="21"/>
+      <c r="I73" s="22"/>
     </row>
     <row r="74" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="1">
@@ -2283,7 +2284,7 @@
       <c r="E74" t="s">
         <v>6</v>
       </c>
-      <c r="I74" s="21"/>
+      <c r="I74" s="22"/>
     </row>
     <row r="75" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="3">
@@ -2298,7 +2299,7 @@
       <c r="E75" t="s">
         <v>6</v>
       </c>
-      <c r="I75" s="21"/>
+      <c r="I75" s="22"/>
     </row>
     <row r="76" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="3">
@@ -2313,7 +2314,7 @@
       <c r="E76" t="s">
         <v>6</v>
       </c>
-      <c r="I76" s="21"/>
+      <c r="I76" s="22"/>
     </row>
     <row r="77" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="3">
@@ -2328,22 +2329,25 @@
       <c r="E77" t="s">
         <v>6</v>
       </c>
-      <c r="I77" s="21"/>
+      <c r="I77" s="22"/>
     </row>
     <row r="78" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A78" s="3">
-        <v>24</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>80</v>
+      <c r="A78" s="1">
+        <v>44</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C78" t="s">
+        <v>13</v>
       </c>
       <c r="D78" s="8">
         <v>77</v>
       </c>
-      <c r="E78" t="s">
+      <c r="E78" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="I78" s="21"/>
+      <c r="I78" s="22"/>
     </row>
     <row r="79" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="3">
@@ -2358,7 +2362,7 @@
       <c r="E79" t="s">
         <v>6</v>
       </c>
-      <c r="I79" s="21"/>
+      <c r="I79" s="22"/>
     </row>
     <row r="80" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="3">
@@ -2373,7 +2377,7 @@
       <c r="E80" t="s">
         <v>6</v>
       </c>
-      <c r="I80" s="21"/>
+      <c r="I80" s="22"/>
     </row>
     <row r="81" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" s="2">
@@ -2388,7 +2392,7 @@
       <c r="E81" t="s">
         <v>4</v>
       </c>
-      <c r="I81" s="21"/>
+      <c r="I81" s="22"/>
     </row>
     <row r="82" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" s="3">
@@ -2403,7 +2407,7 @@
       <c r="E82" t="s">
         <v>6</v>
       </c>
-      <c r="I82" s="21"/>
+      <c r="I82" s="22"/>
     </row>
     <row r="83" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A83" s="3">
@@ -2418,7 +2422,7 @@
       <c r="E83" t="s">
         <v>14</v>
       </c>
-      <c r="I83" s="21"/>
+      <c r="I83" s="22"/>
     </row>
     <row r="84" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84" s="3">
@@ -2433,7 +2437,7 @@
       <c r="E84" t="s">
         <v>14</v>
       </c>
-      <c r="I84" s="21"/>
+      <c r="I84" s="22"/>
     </row>
     <row r="85" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A85" s="3">
@@ -2451,7 +2455,7 @@
       <c r="E85" t="s">
         <v>14</v>
       </c>
-      <c r="I85" s="21"/>
+      <c r="I85" s="22"/>
     </row>
     <row r="86" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="3">
@@ -2466,7 +2470,7 @@
       <c r="E86" t="s">
         <v>1</v>
       </c>
-      <c r="I86" s="21"/>
+      <c r="I86" s="22"/>
     </row>
     <row r="87" spans="1:9" s="4" customFormat="1" ht="13" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A87" s="6"/>
@@ -2481,7 +2485,7 @@
       <c r="F87" s="6"/>
       <c r="G87" s="6"/>
       <c r="H87" s="6"/>
-      <c r="I87" s="22"/>
+      <c r="I87" s="23"/>
     </row>
     <row r="88" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="3">
@@ -2496,7 +2500,7 @@
       <c r="E88" t="s">
         <v>6</v>
       </c>
-      <c r="I88" s="17" t="s">
+      <c r="I88" s="18" t="s">
         <v>132</v>
       </c>
     </row>
@@ -2513,7 +2517,7 @@
       <c r="E89" t="s">
         <v>6</v>
       </c>
-      <c r="I89" s="18"/>
+      <c r="I89" s="19"/>
     </row>
     <row r="90" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90" s="1">
@@ -2528,7 +2532,7 @@
       <c r="E90" t="s">
         <v>6</v>
       </c>
-      <c r="I90" s="18"/>
+      <c r="I90" s="19"/>
     </row>
     <row r="91" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A91" s="1">
@@ -2546,7 +2550,7 @@
       <c r="E91" t="s">
         <v>6</v>
       </c>
-      <c r="I91" s="18"/>
+      <c r="I91" s="19"/>
     </row>
     <row r="92" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A92" s="1">
@@ -2564,7 +2568,7 @@
       <c r="E92" t="s">
         <v>6</v>
       </c>
-      <c r="I92" s="18"/>
+      <c r="I92" s="19"/>
     </row>
     <row r="93" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A93" s="1">
@@ -2579,7 +2583,7 @@
       <c r="E93" t="s">
         <v>6</v>
       </c>
-      <c r="I93" s="18"/>
+      <c r="I93" s="19"/>
     </row>
     <row r="94" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A94" s="1">
@@ -2594,7 +2598,7 @@
       <c r="E94" t="s">
         <v>6</v>
       </c>
-      <c r="I94" s="18"/>
+      <c r="I94" s="19"/>
     </row>
     <row r="95" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A95" s="3">
@@ -2612,7 +2616,7 @@
       <c r="E95" t="s">
         <v>14</v>
       </c>
-      <c r="I95" s="18"/>
+      <c r="I95" s="19"/>
     </row>
     <row r="96" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A96" s="3">
@@ -2627,7 +2631,7 @@
       <c r="E96" t="s">
         <v>6</v>
       </c>
-      <c r="I96" s="18"/>
+      <c r="I96" s="19"/>
     </row>
     <row r="97" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A97" s="3">
@@ -2642,7 +2646,7 @@
       <c r="E97" t="s">
         <v>6</v>
       </c>
-      <c r="I97" s="18"/>
+      <c r="I97" s="19"/>
     </row>
     <row r="98" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A98" s="1">
@@ -2660,7 +2664,7 @@
       <c r="E98" t="s">
         <v>1</v>
       </c>
-      <c r="I98" s="18"/>
+      <c r="I98" s="19"/>
     </row>
     <row r="99" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A99" s="1">
@@ -2675,7 +2679,7 @@
       <c r="E99" t="s">
         <v>1</v>
       </c>
-      <c r="I99" s="18"/>
+      <c r="I99" s="19"/>
     </row>
     <row r="100" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A100" s="1">
@@ -2690,7 +2694,7 @@
       <c r="E100" t="s">
         <v>1</v>
       </c>
-      <c r="I100" s="18"/>
+      <c r="I100" s="19"/>
     </row>
     <row r="101" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A101" s="1">
@@ -2705,7 +2709,7 @@
       <c r="E101" t="s">
         <v>1</v>
       </c>
-      <c r="I101" s="18"/>
+      <c r="I101" s="19"/>
     </row>
     <row r="102" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A102" s="1">
@@ -2723,7 +2727,7 @@
       <c r="E102" t="s">
         <v>1</v>
       </c>
-      <c r="I102" s="18"/>
+      <c r="I102" s="19"/>
     </row>
     <row r="103" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A103" s="2">
@@ -2738,7 +2742,7 @@
       <c r="E103" t="s">
         <v>1</v>
       </c>
-      <c r="I103" s="18"/>
+      <c r="I103" s="19"/>
     </row>
     <row r="104" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A104" s="3">
@@ -2753,7 +2757,7 @@
       <c r="E104" t="s">
         <v>1</v>
       </c>
-      <c r="I104" s="18"/>
+      <c r="I104" s="19"/>
     </row>
     <row r="105" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A105" s="3">
@@ -2768,7 +2772,7 @@
       <c r="E105" t="s">
         <v>1</v>
       </c>
-      <c r="I105" s="18"/>
+      <c r="I105" s="19"/>
     </row>
     <row r="106" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A106" s="3">
@@ -2783,7 +2787,7 @@
       <c r="E106" t="s">
         <v>1</v>
       </c>
-      <c r="I106" s="18"/>
+      <c r="I106" s="19"/>
     </row>
     <row r="107" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A107" s="3">
@@ -2798,7 +2802,7 @@
       <c r="E107" t="s">
         <v>1</v>
       </c>
-      <c r="I107" s="18"/>
+      <c r="I107" s="19"/>
     </row>
     <row r="108" spans="1:9" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A108" s="1">
@@ -2813,7 +2817,7 @@
       <c r="E108" t="s">
         <v>1</v>
       </c>
-      <c r="I108" s="18"/>
+      <c r="I108" s="19"/>
     </row>
     <row r="109" spans="1:9" s="4" customFormat="1" ht="13" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A109" s="12">
@@ -2828,7 +2832,7 @@
       <c r="E109" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="I109" s="19"/>
+      <c r="I109" s="20"/>
     </row>
     <row r="110" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A110" s="1">
@@ -2843,7 +2847,7 @@
       <c r="E110" t="s">
         <v>1</v>
       </c>
-      <c r="I110" s="20" t="s">
+      <c r="I110" s="21" t="s">
         <v>134</v>
       </c>
     </row>
@@ -2860,7 +2864,7 @@
       <c r="E111" t="s">
         <v>1</v>
       </c>
-      <c r="I111" s="21"/>
+      <c r="I111" s="22"/>
     </row>
     <row r="112" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A112" s="2">
@@ -2875,7 +2879,7 @@
       <c r="E112" t="s">
         <v>1</v>
       </c>
-      <c r="I112" s="21"/>
+      <c r="I112" s="22"/>
     </row>
     <row r="113" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A113" s="3">
@@ -2890,7 +2894,7 @@
       <c r="E113" t="s">
         <v>1</v>
       </c>
-      <c r="I113" s="21"/>
+      <c r="I113" s="22"/>
     </row>
     <row r="114" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A114" s="3">
@@ -2905,7 +2909,7 @@
       <c r="E114" t="s">
         <v>1</v>
       </c>
-      <c r="I114" s="21"/>
+      <c r="I114" s="22"/>
     </row>
     <row r="115" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A115" s="3">
@@ -2920,7 +2924,7 @@
       <c r="E115" t="s">
         <v>1</v>
       </c>
-      <c r="I115" s="21"/>
+      <c r="I115" s="22"/>
     </row>
     <row r="116" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A116" s="1">
@@ -2935,7 +2939,7 @@
       <c r="E116" t="s">
         <v>1</v>
       </c>
-      <c r="I116" s="21"/>
+      <c r="I116" s="22"/>
     </row>
     <row r="117" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A117" s="1">
@@ -2950,7 +2954,7 @@
       <c r="E117" t="s">
         <v>1</v>
       </c>
-      <c r="I117" s="21"/>
+      <c r="I117" s="22"/>
     </row>
     <row r="118" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A118" s="1">
@@ -2965,7 +2969,7 @@
       <c r="E118" t="s">
         <v>1</v>
       </c>
-      <c r="I118" s="21"/>
+      <c r="I118" s="22"/>
     </row>
     <row r="119" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A119" s="1">
@@ -2980,7 +2984,7 @@
       <c r="E119" t="s">
         <v>1</v>
       </c>
-      <c r="I119" s="21"/>
+      <c r="I119" s="22"/>
     </row>
     <row r="120" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A120" s="1">
@@ -2998,7 +3002,7 @@
       <c r="E120" t="s">
         <v>1</v>
       </c>
-      <c r="I120" s="21"/>
+      <c r="I120" s="22"/>
     </row>
     <row r="121" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A121" s="1">
@@ -3013,13 +3017,13 @@
       <c r="E121" t="s">
         <v>1</v>
       </c>
-      <c r="I121" s="21"/>
+      <c r="I121" s="22"/>
     </row>
     <row r="122" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A122" s="3">
         <v>69</v>
       </c>
-      <c r="B122" s="23" t="s">
+      <c r="B122" s="17" t="s">
         <v>148</v>
       </c>
       <c r="D122" s="8">
@@ -3028,7 +3032,7 @@
       <c r="E122" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="I122" s="21"/>
+      <c r="I122" s="22"/>
     </row>
     <row r="123" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A123" s="1">
@@ -3043,7 +3047,7 @@
       <c r="E123" t="s">
         <v>1</v>
       </c>
-      <c r="I123" s="21"/>
+      <c r="I123" s="22"/>
     </row>
     <row r="124" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A124" s="1">
@@ -3061,7 +3065,7 @@
       <c r="E124" t="s">
         <v>1</v>
       </c>
-      <c r="I124" s="21"/>
+      <c r="I124" s="22"/>
     </row>
     <row r="125" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A125" s="1">
@@ -3076,7 +3080,7 @@
       <c r="E125" t="s">
         <v>1</v>
       </c>
-      <c r="I125" s="21"/>
+      <c r="I125" s="22"/>
     </row>
     <row r="126" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A126" s="2">
@@ -3091,7 +3095,7 @@
       <c r="E126" t="s">
         <v>1</v>
       </c>
-      <c r="I126" s="21"/>
+      <c r="I126" s="22"/>
     </row>
     <row r="127" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A127" s="3">
@@ -3106,7 +3110,7 @@
       <c r="E127" t="s">
         <v>1</v>
       </c>
-      <c r="I127" s="21"/>
+      <c r="I127" s="22"/>
     </row>
     <row r="128" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A128" s="3">
@@ -3121,7 +3125,7 @@
       <c r="E128" t="s">
         <v>1</v>
       </c>
-      <c r="I128" s="21"/>
+      <c r="I128" s="22"/>
     </row>
     <row r="129" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A129" s="3">
@@ -3139,7 +3143,7 @@
       <c r="E129" t="s">
         <v>1</v>
       </c>
-      <c r="I129" s="21"/>
+      <c r="I129" s="22"/>
     </row>
     <row r="130" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A130" s="2">
@@ -3154,7 +3158,7 @@
       <c r="E130" t="s">
         <v>1</v>
       </c>
-      <c r="I130" s="21"/>
+      <c r="I130" s="22"/>
     </row>
     <row r="131" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A131" s="3">
@@ -3172,7 +3176,7 @@
       <c r="E131" t="s">
         <v>1</v>
       </c>
-      <c r="I131" s="21"/>
+      <c r="I131" s="22"/>
     </row>
     <row r="132" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A132" s="3">
@@ -3187,7 +3191,7 @@
       <c r="E132" t="s">
         <v>1</v>
       </c>
-      <c r="I132" s="21"/>
+      <c r="I132" s="22"/>
     </row>
     <row r="133" spans="1:9" s="4" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A133" s="6"/>
@@ -3202,7 +3206,7 @@
       <c r="F133" s="6"/>
       <c r="G133" s="6"/>
       <c r="H133" s="6"/>
-      <c r="I133" s="22"/>
+      <c r="I133" s="23"/>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A135" s="1"/>

--- a/STAIX2026/assets/Poster-Presentation-Label-Assignment.xlsx
+++ b/STAIX2026/assets/Poster-Presentation-Label-Assignment.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tracyke/Dropbox/Mac (2)/Documents/2026/STAI-X conference/Poster session/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DC0A504-326B-7043-8FEF-48FC2A381FCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDFAC521-8B32-384B-A109-C43FC5BF8454}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -188,9 +188,6 @@
     <t>Association-Preserving Longitudinal Biomarker Imputation with Trajectory- and Outcome-Aware BRITS for Liver Fibrosis Outcome Modeling</t>
   </si>
   <si>
-    <t>Learning Dynamic Brain Connectome Structures from Longitudinal Neuroimaging Data: The L-COSIE Framework</t>
-  </si>
-  <si>
     <t xml:space="preserve">A Transformative TSMOTE extension for Imbalanced Time Series Classification </t>
   </si>
   <si>
@@ -483,6 +480,9 @@
   </si>
   <si>
     <t>The ATLAS Penalty: Auxiliary-Transformed Location-Aware Smoothing with Applications to Spatial Transcriptomics</t>
+  </si>
+  <si>
+    <t>43-44</t>
   </si>
 </sst>
 </file>
@@ -603,7 +603,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
@@ -622,7 +622,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -642,7 +641,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -892,13 +893,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>12700</xdr:colOff>
-      <xdr:row>138</xdr:row>
+      <xdr:row>137</xdr:row>
       <xdr:rowOff>12700</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>266699</xdr:colOff>
-      <xdr:row>182</xdr:row>
+      <xdr:row>181</xdr:row>
       <xdr:rowOff>113505</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1132,7 +1133,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D22663D-DF04-F34F-B5CE-C0BD0EE02426}">
-  <dimension ref="A1:I137"/>
+  <dimension ref="A1:I136"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10.6640625" customWidth="1"/>
@@ -1144,19 +1145,19 @@
   <sheetData>
     <row r="1" spans="1:9" s="4" customFormat="1" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A1" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="C1" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="D1" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="E1" s="11" t="s">
         <v>128</v>
-      </c>
-      <c r="E1" s="11" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
@@ -1172,11 +1173,11 @@
       <c r="E2" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="18" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I2" s="17" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="1">
         <v>43</v>
       </c>
@@ -1189,9 +1190,9 @@
       <c r="E3" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="19"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I3" s="23"/>
+    </row>
+    <row r="4" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="1">
         <v>84</v>
       </c>
@@ -1207,9 +1208,9 @@
       <c r="E4" t="s">
         <v>4</v>
       </c>
-      <c r="I4" s="19"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I4" s="23"/>
+    </row>
+    <row r="5" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="2">
         <v>22</v>
       </c>
@@ -1222,9 +1223,9 @@
       <c r="E5" t="s">
         <v>4</v>
       </c>
-      <c r="I5" s="19"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I5" s="23"/>
+    </row>
+    <row r="6" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="2">
         <v>28</v>
       </c>
@@ -1237,14 +1238,14 @@
       <c r="E6" t="s">
         <v>4</v>
       </c>
-      <c r="I6" s="19"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I6" s="23"/>
+    </row>
+    <row r="7" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="3">
         <v>11</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D7" s="8">
         <v>6</v>
@@ -1252,14 +1253,14 @@
       <c r="E7" t="s">
         <v>4</v>
       </c>
-      <c r="I7" s="19"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I7" s="23"/>
+    </row>
+    <row r="8" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="3">
         <v>15</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D8" s="8">
         <v>7</v>
@@ -1267,14 +1268,14 @@
       <c r="E8" t="s">
         <v>4</v>
       </c>
-      <c r="I8" s="19"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I8" s="23"/>
+    </row>
+    <row r="9" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="3">
         <v>39</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D9" s="8">
         <v>8</v>
@@ -1282,14 +1283,14 @@
       <c r="E9" t="s">
         <v>4</v>
       </c>
-      <c r="I9" s="19"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I9" s="23"/>
+    </row>
+    <row r="10" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="3">
         <v>58</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D10" s="8">
         <v>9</v>
@@ -1297,9 +1298,9 @@
       <c r="E10" t="s">
         <v>4</v>
       </c>
-      <c r="I10" s="19"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I10" s="23"/>
+    </row>
+    <row r="11" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="1">
         <v>119</v>
       </c>
@@ -1312,9 +1313,9 @@
       <c r="E11" t="s">
         <v>4</v>
       </c>
-      <c r="I11" s="19"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I11" s="23"/>
+    </row>
+    <row r="12" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="1">
         <v>130</v>
       </c>
@@ -1322,7 +1323,7 @@
         <v>41</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D12" s="8">
         <v>11</v>
@@ -1330,14 +1331,14 @@
       <c r="E12" t="s">
         <v>4</v>
       </c>
-      <c r="I12" s="19"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I12" s="23"/>
+    </row>
+    <row r="13" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="3">
         <v>63</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D13" s="8">
         <v>12</v>
@@ -1345,14 +1346,14 @@
       <c r="E13" t="s">
         <v>4</v>
       </c>
-      <c r="I13" s="19"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I13" s="23"/>
+    </row>
+    <row r="14" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="3">
         <v>64</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D14" s="8">
         <v>13</v>
@@ -1360,14 +1361,14 @@
       <c r="E14" t="s">
         <v>4</v>
       </c>
-      <c r="I14" s="19"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I14" s="23"/>
+    </row>
+    <row r="15" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="3">
         <v>68</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D15" s="8">
         <v>14</v>
@@ -1375,14 +1376,14 @@
       <c r="E15" t="s">
         <v>4</v>
       </c>
-      <c r="I15" s="19"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I15" s="23"/>
+    </row>
+    <row r="16" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="3">
         <v>71</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D16" s="8">
         <v>15</v>
@@ -1390,14 +1391,14 @@
       <c r="E16" t="s">
         <v>4</v>
       </c>
-      <c r="I16" s="19"/>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I16" s="23"/>
+    </row>
+    <row r="17" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="3">
         <v>75</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D17" s="8">
         <v>16</v>
@@ -1405,9 +1406,9 @@
       <c r="E17" t="s">
         <v>4</v>
       </c>
-      <c r="I17" s="19"/>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I17" s="23"/>
+    </row>
+    <row r="18" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="1">
         <v>29</v>
       </c>
@@ -1420,9 +1421,9 @@
       <c r="E18" t="s">
         <v>8</v>
       </c>
-      <c r="I18" s="19"/>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I18" s="23"/>
+    </row>
+    <row r="19" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="1">
         <v>78</v>
       </c>
@@ -1435,9 +1436,9 @@
       <c r="E19" t="s">
         <v>8</v>
       </c>
-      <c r="I19" s="19"/>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I19" s="23"/>
+    </row>
+    <row r="20" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="1">
         <v>91</v>
       </c>
@@ -1450,9 +1451,9 @@
       <c r="E20" t="s">
         <v>8</v>
       </c>
-      <c r="I20" s="19"/>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I20" s="23"/>
+    </row>
+    <row r="21" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="2">
         <v>35</v>
       </c>
@@ -1465,14 +1466,14 @@
       <c r="E21" t="s">
         <v>8</v>
       </c>
-      <c r="I21" s="19"/>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I21" s="23"/>
+    </row>
+    <row r="22" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="3">
         <v>1</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D22" s="8">
         <v>21</v>
@@ -1480,14 +1481,14 @@
       <c r="E22" t="s">
         <v>8</v>
       </c>
-      <c r="I22" s="19"/>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I22" s="23"/>
+    </row>
+    <row r="23" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="3">
         <v>2</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D23" s="8">
         <v>22</v>
@@ -1495,14 +1496,14 @@
       <c r="E23" t="s">
         <v>8</v>
       </c>
-      <c r="I23" s="19"/>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I23" s="23"/>
+    </row>
+    <row r="24" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="3">
         <v>19</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D24" s="8">
         <v>23</v>
@@ -1510,17 +1511,17 @@
       <c r="E24" t="s">
         <v>8</v>
       </c>
-      <c r="I24" s="19"/>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I24" s="23"/>
+    </row>
+    <row r="25" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="3">
         <v>35</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C25" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D25" s="8">
         <v>24</v>
@@ -1528,14 +1529,14 @@
       <c r="E25" t="s">
         <v>8</v>
       </c>
-      <c r="I25" s="19"/>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I25" s="23"/>
+    </row>
+    <row r="26" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="2">
         <v>106</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D26" s="8">
         <v>25</v>
@@ -1543,9 +1544,9 @@
       <c r="E26" t="s">
         <v>8</v>
       </c>
-      <c r="I26" s="19"/>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I26" s="23"/>
+    </row>
+    <row r="27" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="1">
         <v>101</v>
       </c>
@@ -1561,7 +1562,7 @@
       <c r="E27" t="s">
         <v>8</v>
       </c>
-      <c r="I27" s="19"/>
+      <c r="I27" s="23"/>
     </row>
     <row r="28" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="1">
@@ -1576,17 +1577,17 @@
       <c r="E28" t="s">
         <v>8</v>
       </c>
-      <c r="I28" s="19"/>
+      <c r="I28" s="23"/>
     </row>
     <row r="29" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="3">
         <v>38</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C29" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D29" s="8">
         <v>28</v>
@@ -1594,14 +1595,14 @@
       <c r="E29" t="s">
         <v>8</v>
       </c>
-      <c r="I29" s="19"/>
+      <c r="I29" s="23"/>
     </row>
     <row r="30" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="3">
         <v>67</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D30" s="8">
         <v>29</v>
@@ -1609,14 +1610,14 @@
       <c r="E30" t="s">
         <v>8</v>
       </c>
-      <c r="I30" s="19"/>
+      <c r="I30" s="23"/>
     </row>
     <row r="31" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="3">
         <v>77</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D31" s="8">
         <v>30</v>
@@ -1624,14 +1625,14 @@
       <c r="E31" t="s">
         <v>8</v>
       </c>
-      <c r="I31" s="19"/>
+      <c r="I31" s="23"/>
     </row>
     <row r="32" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="3">
         <v>78</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D32" s="8">
         <v>31</v>
@@ -1639,7 +1640,7 @@
       <c r="E32" t="s">
         <v>8</v>
       </c>
-      <c r="I32" s="19"/>
+      <c r="I32" s="23"/>
     </row>
     <row r="33" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="2">
@@ -1654,14 +1655,14 @@
       <c r="E33" t="s">
         <v>8</v>
       </c>
-      <c r="I33" s="19"/>
+      <c r="I33" s="23"/>
     </row>
     <row r="34" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="3">
         <v>22</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D34" s="8">
         <v>33</v>
@@ -1669,14 +1670,14 @@
       <c r="E34" t="s">
         <v>14</v>
       </c>
-      <c r="I34" s="19"/>
+      <c r="I34" s="23"/>
     </row>
     <row r="35" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="1">
         <v>115</v>
       </c>
-      <c r="B35" s="24" t="s">
-        <v>149</v>
+      <c r="B35" s="1" t="s">
+        <v>148</v>
       </c>
       <c r="D35" s="8">
         <v>34</v>
@@ -1684,7 +1685,7 @@
       <c r="E35" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="I35" s="19"/>
+      <c r="I35" s="23"/>
     </row>
     <row r="36" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="1">
@@ -1699,7 +1700,7 @@
       <c r="E36" t="s">
         <v>14</v>
       </c>
-      <c r="I36" s="19"/>
+      <c r="I36" s="23"/>
     </row>
     <row r="37" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="1">
@@ -1714,7 +1715,7 @@
       <c r="E37" t="s">
         <v>14</v>
       </c>
-      <c r="I37" s="19"/>
+      <c r="I37" s="23"/>
     </row>
     <row r="38" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="2">
@@ -1729,32 +1730,32 @@
       <c r="E38" t="s">
         <v>14</v>
       </c>
-      <c r="I38" s="19"/>
+      <c r="I38" s="23"/>
     </row>
     <row r="39" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A39" s="2">
-        <v>46</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>51</v>
+      <c r="A39" s="3">
+        <v>3</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C39" t="s">
+        <v>66</v>
       </c>
       <c r="D39" s="8">
         <v>38</v>
       </c>
-      <c r="E39" t="s">
-        <v>14</v>
-      </c>
-      <c r="I39" s="19"/>
+      <c r="E39" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="I39" s="23"/>
     </row>
     <row r="40" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="3">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C40" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D40" s="8">
         <v>39</v>
@@ -1762,14 +1763,14 @@
       <c r="E40" t="s">
         <v>14</v>
       </c>
-      <c r="I40" s="19"/>
+      <c r="I40" s="23"/>
     </row>
     <row r="41" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="3">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D41" s="8">
         <v>40</v>
@@ -1777,14 +1778,14 @@
       <c r="E41" t="s">
         <v>14</v>
       </c>
-      <c r="I41" s="19"/>
+      <c r="I41" s="23"/>
     </row>
     <row r="42" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="3">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="D42" s="8">
         <v>41</v>
@@ -1792,14 +1793,14 @@
       <c r="E42" t="s">
         <v>14</v>
       </c>
-      <c r="I42" s="19"/>
+      <c r="I42" s="23"/>
     </row>
     <row r="43" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="3">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D43" s="8">
         <v>42</v>
@@ -1807,1434 +1808,1422 @@
       <c r="E43" t="s">
         <v>14</v>
       </c>
-      <c r="I43" s="19"/>
-    </row>
-    <row r="44" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A44" s="3">
-        <v>37</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D44" s="8">
-        <v>43</v>
-      </c>
-      <c r="E44" t="s">
-        <v>14</v>
-      </c>
+      <c r="I43" s="23"/>
+    </row>
+    <row r="44" spans="1:9" s="4" customFormat="1" ht="13" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="15"/>
+      <c r="B44" s="15"/>
+      <c r="C44" s="15"/>
+      <c r="D44" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="E44" s="15"/>
+      <c r="F44" s="15"/>
+      <c r="G44" s="15"/>
+      <c r="H44" s="15"/>
       <c r="I44" s="19"/>
     </row>
-    <row r="45" spans="1:9" s="4" customFormat="1" ht="13" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="15"/>
-      <c r="B45" s="15"/>
-      <c r="C45" s="15"/>
-      <c r="D45" s="16">
-        <v>44</v>
-      </c>
-      <c r="E45" s="15"/>
-      <c r="F45" s="15"/>
-      <c r="G45" s="15"/>
-      <c r="H45" s="15"/>
-      <c r="I45" s="20"/>
+    <row r="45" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A45" s="3">
+        <v>40</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D45" s="8">
+        <v>45</v>
+      </c>
+      <c r="E45" t="s">
+        <v>14</v>
+      </c>
+      <c r="I45" s="20" t="s">
+        <v>130</v>
+      </c>
     </row>
     <row r="46" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="3">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D46" s="8">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E46" t="s">
         <v>14</v>
       </c>
-      <c r="I46" s="21" t="s">
-        <v>131</v>
-      </c>
+      <c r="I46" s="21"/>
     </row>
     <row r="47" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A47" s="3">
-        <v>45</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>93</v>
+      <c r="A47" s="1">
+        <v>60</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="D47" s="8">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E47" t="s">
         <v>14</v>
       </c>
-      <c r="I47" s="22"/>
+      <c r="I47" s="21"/>
     </row>
     <row r="48" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="1">
-        <v>60</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
+      </c>
+      <c r="B48" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="C48" s="13" t="s">
+        <v>137</v>
       </c>
       <c r="D48" s="8">
-        <v>47</v>
-      </c>
-      <c r="E48" t="s">
-        <v>14</v>
-      </c>
-      <c r="I48" s="22"/>
+        <v>48</v>
+      </c>
+      <c r="E48" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="I48" s="21"/>
     </row>
     <row r="49" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="1">
-        <v>32</v>
-      </c>
-      <c r="B49" s="14" t="s">
-        <v>147</v>
+        <v>93</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>30</v>
       </c>
       <c r="D49" s="8">
-        <v>48</v>
-      </c>
-      <c r="E49" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="I49" s="22"/>
+        <v>49</v>
+      </c>
+      <c r="E49" t="s">
+        <v>14</v>
+      </c>
+      <c r="I49" s="21"/>
     </row>
     <row r="50" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="1">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D50" s="8">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E50" t="s">
         <v>14</v>
       </c>
-      <c r="I50" s="22"/>
+      <c r="I50" s="21"/>
     </row>
     <row r="51" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A51" s="1">
-        <v>107</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>33</v>
+      <c r="A51" s="2">
+        <v>75</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>55</v>
       </c>
       <c r="D51" s="8">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E51" t="s">
         <v>14</v>
       </c>
-      <c r="I51" s="22"/>
+      <c r="I51" s="21"/>
     </row>
     <row r="52" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>56</v>
       </c>
       <c r="D52" s="8">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E52" t="s">
         <v>14</v>
       </c>
-      <c r="I52" s="22"/>
+      <c r="I52" s="21"/>
     </row>
     <row r="53" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A53" s="2">
-        <v>96</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>57</v>
+      <c r="A53" s="3">
+        <v>48</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C53" t="s">
+        <v>66</v>
       </c>
       <c r="D53" s="8">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E53" t="s">
         <v>14</v>
       </c>
-      <c r="I53" s="22"/>
+      <c r="I53" s="21"/>
     </row>
     <row r="54" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="3">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="C54" t="s">
-        <v>67</v>
-      </c>
       <c r="D54" s="8">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E54" t="s">
         <v>14</v>
       </c>
-      <c r="I54" s="22"/>
+      <c r="I54" s="21"/>
     </row>
     <row r="55" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="3">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D55" s="8">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E55" t="s">
         <v>14</v>
       </c>
-      <c r="I55" s="22"/>
+      <c r="I55" s="21"/>
     </row>
     <row r="56" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="3">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D56" s="8">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E56" t="s">
         <v>14</v>
       </c>
-      <c r="I56" s="22"/>
+      <c r="I56" s="21"/>
     </row>
     <row r="57" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="3">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="D57" s="8">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E57" t="s">
         <v>14</v>
       </c>
-      <c r="I57" s="22"/>
+      <c r="I57" s="21"/>
     </row>
     <row r="58" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="3">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D58" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E58" t="s">
         <v>14</v>
       </c>
-      <c r="I58" s="22"/>
+      <c r="I58" s="21"/>
     </row>
     <row r="59" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="3">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>112</v>
+        <v>141</v>
       </c>
       <c r="D59" s="8">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E59" t="s">
-        <v>14</v>
-      </c>
-      <c r="I59" s="22"/>
+        <v>6</v>
+      </c>
+      <c r="I59" s="21"/>
     </row>
     <row r="60" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A60" s="3">
-        <v>50</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>142</v>
+      <c r="A60" s="1">
+        <v>143</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C60" t="s">
+        <v>13</v>
       </c>
       <c r="D60" s="8">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E60" t="s">
-        <v>6</v>
-      </c>
-      <c r="I60" s="22"/>
+        <v>14</v>
+      </c>
+      <c r="I60" s="21"/>
     </row>
     <row r="61" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A61" s="1">
-        <v>143</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C61" t="s">
-        <v>13</v>
+      <c r="A61" s="3">
+        <v>83</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>121</v>
       </c>
       <c r="D61" s="8">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E61" t="s">
         <v>14</v>
       </c>
-      <c r="I61" s="22"/>
+      <c r="I61" s="21"/>
     </row>
     <row r="62" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="3">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D62" s="8">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E62" t="s">
         <v>14</v>
       </c>
-      <c r="I62" s="22"/>
+      <c r="I62" s="21"/>
     </row>
     <row r="63" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="3">
-        <v>87</v>
+        <v>34</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="D63" s="8">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E63" t="s">
-        <v>14</v>
-      </c>
-      <c r="I63" s="22"/>
-    </row>
-    <row r="64" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+        <v>6</v>
+      </c>
+      <c r="I63" s="21"/>
+    </row>
+    <row r="64" spans="1:9" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="3">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>143</v>
+        <v>94</v>
+      </c>
+      <c r="C64" t="s">
+        <v>66</v>
       </c>
       <c r="D64" s="8">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E64" t="s">
         <v>6</v>
       </c>
-      <c r="I64" s="22"/>
-    </row>
-    <row r="65" spans="1:9" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="I64" s="21"/>
+    </row>
+    <row r="65" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="3">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="C65" t="s">
-        <v>67</v>
+        <v>99</v>
       </c>
       <c r="D65" s="8">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E65" t="s">
         <v>6</v>
       </c>
-      <c r="I65" s="22"/>
+      <c r="I65" s="21"/>
     </row>
     <row r="66" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="3">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D66" s="8">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E66" t="s">
         <v>6</v>
       </c>
-      <c r="I66" s="22"/>
+      <c r="I66" s="21"/>
     </row>
     <row r="67" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="3">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D67" s="8">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E67" t="s">
         <v>6</v>
       </c>
-      <c r="I67" s="22"/>
+      <c r="I67" s="21"/>
     </row>
     <row r="68" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A68" s="3">
-        <v>65</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>107</v>
+      <c r="A68" s="2">
+        <v>103</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>58</v>
       </c>
       <c r="D68" s="8">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E68" t="s">
         <v>6</v>
       </c>
-      <c r="I68" s="22"/>
+      <c r="I68" s="21"/>
     </row>
     <row r="69" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="2">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D69" s="8">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E69" t="s">
         <v>6</v>
       </c>
-      <c r="I69" s="22"/>
+      <c r="I69" s="21"/>
     </row>
     <row r="70" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A70" s="2">
-        <v>111</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>61</v>
+      <c r="A70" s="3">
+        <v>65</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>107</v>
       </c>
       <c r="D70" s="8">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E70" t="s">
         <v>6</v>
       </c>
-      <c r="I70" s="22"/>
+      <c r="I70" s="21"/>
     </row>
     <row r="71" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A71" s="3">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="D71" s="8">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E71" t="s">
         <v>6</v>
       </c>
-      <c r="I71" s="22"/>
+      <c r="I71" s="21"/>
     </row>
     <row r="72" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="3">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D72" s="8">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E72" t="s">
         <v>6</v>
       </c>
-      <c r="I72" s="22"/>
+      <c r="I72" s="21"/>
     </row>
     <row r="73" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A73" s="3">
-        <v>81</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>120</v>
+      <c r="A73" s="1">
+        <v>113</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C73" s="13" t="s">
+        <v>137</v>
       </c>
       <c r="D73" s="8">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E73" t="s">
         <v>6</v>
       </c>
-      <c r="I73" s="22"/>
+      <c r="I73" s="21"/>
     </row>
     <row r="74" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A74" s="1">
-        <v>113</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C74" s="13" t="s">
-        <v>138</v>
+      <c r="A74" s="3">
+        <v>53</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>98</v>
       </c>
       <c r="D74" s="8">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E74" t="s">
         <v>6</v>
       </c>
-      <c r="I74" s="22"/>
+      <c r="I74" s="21"/>
     </row>
     <row r="75" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="3">
-        <v>53</v>
+        <v>7</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>99</v>
+        <v>67</v>
       </c>
       <c r="D75" s="8">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E75" t="s">
         <v>6</v>
       </c>
-      <c r="I75" s="22"/>
+      <c r="I75" s="21"/>
     </row>
     <row r="76" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B76" s="3" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="8">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E76" t="s">
         <v>6</v>
       </c>
-      <c r="I76" s="22"/>
+      <c r="I76" s="21"/>
     </row>
     <row r="77" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A77" s="3">
-        <v>8</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>69</v>
+      <c r="A77" s="1">
+        <v>44</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C77" t="s">
+        <v>13</v>
       </c>
       <c r="D77" s="8">
+        <v>77</v>
+      </c>
+      <c r="E77" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="I77" s="21"/>
+    </row>
+    <row r="78" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A78" s="3">
+        <v>20</v>
+      </c>
+      <c r="B78" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="E77" t="s">
+      <c r="D78" s="8">
+        <v>78</v>
+      </c>
+      <c r="E78" t="s">
         <v>6</v>
       </c>
-      <c r="I77" s="22"/>
-    </row>
-    <row r="78" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A78" s="1">
-        <v>44</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C78" t="s">
-        <v>13</v>
-      </c>
-      <c r="D78" s="8">
-        <v>77</v>
-      </c>
-      <c r="E78" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="I78" s="22"/>
+      <c r="I78" s="21"/>
     </row>
     <row r="79" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="3">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D79" s="8">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E79" t="s">
         <v>6</v>
       </c>
-      <c r="I79" s="22"/>
+      <c r="I79" s="21"/>
     </row>
     <row r="80" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A80" s="3">
-        <v>24</v>
-      </c>
-      <c r="B80" s="3" t="s">
+      <c r="A80" s="2">
+        <v>136</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D80" s="8">
         <v>80</v>
       </c>
-      <c r="D80" s="8">
-        <v>79</v>
-      </c>
       <c r="E80" t="s">
+        <v>4</v>
+      </c>
+      <c r="I80" s="21"/>
+    </row>
+    <row r="81" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A81" s="3">
+        <v>72</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D81" s="8">
+        <v>81</v>
+      </c>
+      <c r="E81" t="s">
         <v>6</v>
       </c>
-      <c r="I80" s="22"/>
-    </row>
-    <row r="81" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A81" s="2">
-        <v>136</v>
-      </c>
-      <c r="B81" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="D81" s="8">
-        <v>80</v>
-      </c>
-      <c r="E81" t="s">
-        <v>4</v>
-      </c>
-      <c r="I81" s="22"/>
+      <c r="I81" s="21"/>
     </row>
     <row r="82" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" s="3">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="D82" s="8">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E82" t="s">
-        <v>6</v>
-      </c>
-      <c r="I82" s="22"/>
+        <v>14</v>
+      </c>
+      <c r="I82" s="21"/>
     </row>
     <row r="83" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A83" s="3">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D83" s="8">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E83" t="s">
         <v>14</v>
       </c>
-      <c r="I83" s="22"/>
+      <c r="I83" s="21"/>
     </row>
     <row r="84" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84" s="3">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>119</v>
+        <v>144</v>
+      </c>
+      <c r="C84" s="13" t="s">
+        <v>66</v>
       </c>
       <c r="D84" s="8">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E84" t="s">
         <v>14</v>
       </c>
-      <c r="I84" s="22"/>
+      <c r="I84" s="21"/>
     </row>
     <row r="85" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A85" s="3">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="B85" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D85" s="8">
+        <v>85</v>
+      </c>
+      <c r="E85" t="s">
+        <v>1</v>
+      </c>
+      <c r="I85" s="21"/>
+    </row>
+    <row r="86" spans="1:9" s="4" customFormat="1" ht="13" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A86" s="6"/>
+      <c r="B86" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="C86" s="6"/>
+      <c r="D86" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="C85" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="D85" s="8">
-        <v>84</v>
-      </c>
-      <c r="E85" t="s">
-        <v>14</v>
-      </c>
-      <c r="I85" s="22"/>
-    </row>
-    <row r="86" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A86" s="3">
-        <v>56</v>
-      </c>
-      <c r="B86" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="D86" s="8">
-        <v>85</v>
-      </c>
-      <c r="E86" t="s">
-        <v>1</v>
-      </c>
+      <c r="E86" s="6"/>
+      <c r="F86" s="6"/>
+      <c r="G86" s="6"/>
+      <c r="H86" s="6"/>
       <c r="I86" s="22"/>
     </row>
-    <row r="87" spans="1:9" s="4" customFormat="1" ht="13" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="6"/>
-      <c r="B87" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="C87" s="6"/>
-      <c r="D87" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="E87" s="6"/>
-      <c r="F87" s="6"/>
-      <c r="G87" s="6"/>
-      <c r="H87" s="6"/>
-      <c r="I87" s="23"/>
+    <row r="87" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A87" s="3">
+        <v>31</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D87" s="8">
+        <v>89</v>
+      </c>
+      <c r="E87" t="s">
+        <v>6</v>
+      </c>
+      <c r="I87" s="17" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="88" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A88" s="3">
-        <v>31</v>
-      </c>
-      <c r="B88" s="3" t="s">
-        <v>83</v>
+      <c r="A88" s="2">
+        <v>58</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>53</v>
       </c>
       <c r="D88" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E88" t="s">
         <v>6</v>
       </c>
-      <c r="I88" s="18" t="s">
-        <v>132</v>
-      </c>
+      <c r="I88" s="18"/>
     </row>
     <row r="89" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A89" s="2">
-        <v>58</v>
-      </c>
-      <c r="B89" s="2" t="s">
-        <v>54</v>
+      <c r="A89" s="1">
+        <v>24</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>5</v>
       </c>
       <c r="D89" s="8">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E89" t="s">
         <v>6</v>
       </c>
-      <c r="I89" s="19"/>
+      <c r="I89" s="18"/>
     </row>
     <row r="90" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90" s="1">
-        <v>24</v>
+        <v>122</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>5</v>
+        <v>37</v>
+      </c>
+      <c r="C90" t="s">
+        <v>13</v>
       </c>
       <c r="D90" s="8">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E90" t="s">
         <v>6</v>
       </c>
-      <c r="I90" s="19"/>
+      <c r="I90" s="18"/>
     </row>
     <row r="91" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A91" s="1">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C91" t="s">
         <v>13</v>
       </c>
       <c r="D91" s="8">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E91" t="s">
         <v>6</v>
       </c>
-      <c r="I91" s="19"/>
+      <c r="I91" s="18"/>
     </row>
     <row r="92" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A92" s="1">
-        <v>132</v>
+        <v>61</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C92" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D92" s="8">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E92" t="s">
         <v>6</v>
       </c>
-      <c r="I92" s="19"/>
+      <c r="I92" s="18"/>
     </row>
     <row r="93" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A93" s="1">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="D93" s="8">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E93" t="s">
         <v>6</v>
       </c>
-      <c r="I93" s="19"/>
+      <c r="I93" s="18"/>
     </row>
     <row r="94" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A94" s="1">
-        <v>38</v>
-      </c>
-      <c r="B94" s="1" t="s">
-        <v>9</v>
+      <c r="A94" s="3">
+        <v>74</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C94" s="13" t="s">
+        <v>66</v>
       </c>
       <c r="D94" s="8">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E94" t="s">
-        <v>6</v>
-      </c>
-      <c r="I94" s="19"/>
+        <v>14</v>
+      </c>
+      <c r="I94" s="18"/>
     </row>
     <row r="95" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A95" s="3">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="C95" s="13" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="D95" s="8">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E95" t="s">
-        <v>14</v>
-      </c>
-      <c r="I95" s="19"/>
+        <v>6</v>
+      </c>
+      <c r="I95" s="18"/>
     </row>
     <row r="96" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A96" s="3">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D96" s="8">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E96" t="s">
         <v>6</v>
       </c>
-      <c r="I96" s="19"/>
+      <c r="I96" s="18"/>
     </row>
     <row r="97" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A97" s="3">
-        <v>46</v>
-      </c>
-      <c r="B97" s="3" t="s">
-        <v>94</v>
+      <c r="A97" s="1">
+        <v>137</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C97" t="s">
+        <v>13</v>
       </c>
       <c r="D97" s="8">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E97" t="s">
-        <v>6</v>
-      </c>
-      <c r="I97" s="19"/>
+        <v>1</v>
+      </c>
+      <c r="I97" s="18"/>
     </row>
     <row r="98" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A98" s="1">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C98" t="s">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="D98" s="8">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E98" t="s">
         <v>1</v>
       </c>
-      <c r="I98" s="19"/>
+      <c r="I98" s="18"/>
     </row>
     <row r="99" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A99" s="1">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D99" s="8">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E99" t="s">
         <v>1</v>
       </c>
-      <c r="I99" s="19"/>
+      <c r="I99" s="18"/>
     </row>
     <row r="100" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A100" s="1">
-        <v>141</v>
+        <v>16</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="D100" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E100" t="s">
         <v>1</v>
       </c>
-      <c r="I100" s="19"/>
+      <c r="I100" s="18"/>
     </row>
     <row r="101" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A101" s="1">
-        <v>16</v>
+        <v>72</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>0</v>
+        <v>23</v>
+      </c>
+      <c r="C101" t="s">
+        <v>13</v>
       </c>
       <c r="D101" s="8">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E101" t="s">
         <v>1</v>
       </c>
-      <c r="I101" s="19"/>
+      <c r="I101" s="18"/>
     </row>
     <row r="102" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A102" s="1">
-        <v>72</v>
-      </c>
-      <c r="B102" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C102" t="s">
-        <v>13</v>
+      <c r="A102" s="2">
+        <v>47</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>51</v>
       </c>
       <c r="D102" s="8">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E102" t="s">
         <v>1</v>
       </c>
-      <c r="I102" s="19"/>
+      <c r="I102" s="18"/>
     </row>
     <row r="103" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A103" s="2">
-        <v>47</v>
-      </c>
-      <c r="B103" s="2" t="s">
-        <v>52</v>
+      <c r="A103" s="3">
+        <v>17</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>73</v>
       </c>
       <c r="D103" s="8">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E103" t="s">
         <v>1</v>
       </c>
-      <c r="I103" s="19"/>
+      <c r="I103" s="18"/>
     </row>
     <row r="104" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A104" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B104" s="3" t="s">
         <v>74</v>
       </c>
       <c r="D104" s="8">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E104" t="s">
         <v>1</v>
       </c>
-      <c r="I104" s="19"/>
+      <c r="I104" s="18"/>
     </row>
     <row r="105" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A105" s="3">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D105" s="8">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E105" t="s">
         <v>1</v>
       </c>
-      <c r="I105" s="19"/>
+      <c r="I105" s="18"/>
     </row>
     <row r="106" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A106" s="3">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B106" s="3" t="s">
         <v>78</v>
       </c>
       <c r="D106" s="8">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E106" t="s">
         <v>1</v>
       </c>
-      <c r="I106" s="19"/>
-    </row>
-    <row r="107" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A107" s="3">
-        <v>23</v>
-      </c>
-      <c r="B107" s="3" t="s">
-        <v>79</v>
+      <c r="I106" s="18"/>
+    </row>
+    <row r="107" spans="1:9" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A107" s="1">
+        <v>65</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="D107" s="8">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E107" t="s">
         <v>1</v>
       </c>
-      <c r="I107" s="19"/>
-    </row>
-    <row r="108" spans="1:9" ht="14" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A108" s="1">
-        <v>65</v>
-      </c>
-      <c r="B108" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D108" s="8">
-        <v>109</v>
-      </c>
-      <c r="E108" t="s">
+      <c r="I107" s="18"/>
+    </row>
+    <row r="108" spans="1:9" s="4" customFormat="1" ht="13" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A108" s="12">
+        <v>70</v>
+      </c>
+      <c r="B108" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D108" s="7">
+        <v>110</v>
+      </c>
+      <c r="E108" s="4" t="s">
         <v>1</v>
       </c>
       <c r="I108" s="19"/>
     </row>
-    <row r="109" spans="1:9" s="4" customFormat="1" ht="13" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A109" s="12">
-        <v>70</v>
-      </c>
-      <c r="B109" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="D109" s="7">
-        <v>110</v>
-      </c>
-      <c r="E109" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="I109" s="20"/>
+    <row r="109" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A109" s="1">
+        <v>80</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D109" s="8">
+        <v>111</v>
+      </c>
+      <c r="E109" t="s">
+        <v>1</v>
+      </c>
+      <c r="I109" s="20" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="110" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A110" s="1">
+        <v>86</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D110" s="8">
+        <v>112</v>
+      </c>
+      <c r="E110" t="s">
+        <v>1</v>
+      </c>
+      <c r="I110" s="21"/>
+    </row>
+    <row r="111" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A111" s="2">
+        <v>47</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D111" s="8">
+        <v>113</v>
+      </c>
+      <c r="E111" t="s">
+        <v>1</v>
+      </c>
+      <c r="I111" s="21"/>
+    </row>
+    <row r="112" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A112" s="3">
+        <v>29</v>
+      </c>
+      <c r="B112" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B110" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D110" s="8">
-        <v>111</v>
-      </c>
-      <c r="E110" t="s">
-        <v>1</v>
-      </c>
-      <c r="I110" s="21" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="111" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A111" s="1">
-        <v>86</v>
-      </c>
-      <c r="B111" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D111" s="8">
-        <v>112</v>
-      </c>
-      <c r="E111" t="s">
-        <v>1</v>
-      </c>
-      <c r="I111" s="22"/>
-    </row>
-    <row r="112" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A112" s="2">
-        <v>47</v>
-      </c>
-      <c r="B112" s="2" t="s">
-        <v>53</v>
-      </c>
       <c r="D112" s="8">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E112" t="s">
         <v>1</v>
       </c>
-      <c r="I112" s="22"/>
+      <c r="I112" s="21"/>
     </row>
     <row r="113" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A113" s="3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B113" s="3" t="s">
         <v>81</v>
       </c>
       <c r="D113" s="8">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E113" t="s">
         <v>1</v>
       </c>
-      <c r="I113" s="22"/>
+      <c r="I113" s="21"/>
     </row>
     <row r="114" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A114" s="3">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D114" s="8">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E114" t="s">
         <v>1</v>
       </c>
-      <c r="I114" s="22"/>
+      <c r="I114" s="21"/>
     </row>
     <row r="115" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A115" s="3">
-        <v>36</v>
-      </c>
-      <c r="B115" s="3" t="s">
-        <v>86</v>
+      <c r="A115" s="1">
+        <v>21</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="D115" s="8">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E115" t="s">
         <v>1</v>
       </c>
-      <c r="I115" s="22"/>
+      <c r="I115" s="21"/>
     </row>
     <row r="116" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A116" s="1">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D116" s="8">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E116" t="s">
         <v>1</v>
       </c>
-      <c r="I116" s="22"/>
+      <c r="I116" s="21"/>
     </row>
     <row r="117" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A117" s="1">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D117" s="8">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E117" t="s">
         <v>1</v>
       </c>
-      <c r="I117" s="22"/>
+      <c r="I117" s="21"/>
     </row>
     <row r="118" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A118" s="1">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D118" s="8">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E118" t="s">
         <v>1</v>
       </c>
-      <c r="I118" s="22"/>
+      <c r="I118" s="21"/>
     </row>
     <row r="119" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A119" s="1">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>18</v>
+        <v>28</v>
+      </c>
+      <c r="C119" t="s">
+        <v>13</v>
       </c>
       <c r="D119" s="8">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E119" t="s">
         <v>1</v>
       </c>
-      <c r="I119" s="22"/>
+      <c r="I119" s="21"/>
     </row>
     <row r="120" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A120" s="1">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C120" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="D120" s="8">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E120" t="s">
         <v>1</v>
       </c>
-      <c r="I120" s="22"/>
+      <c r="I120" s="21"/>
     </row>
     <row r="121" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A121" s="1">
-        <v>105</v>
-      </c>
-      <c r="B121" s="1" t="s">
-        <v>32</v>
+      <c r="A121" s="3">
+        <v>69</v>
+      </c>
+      <c r="B121" s="16" t="s">
+        <v>147</v>
       </c>
       <c r="D121" s="8">
-        <v>122</v>
-      </c>
-      <c r="E121" t="s">
-        <v>1</v>
-      </c>
-      <c r="I121" s="22"/>
+        <v>123</v>
+      </c>
+      <c r="E121" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="I121" s="21"/>
     </row>
     <row r="122" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A122" s="3">
-        <v>69</v>
-      </c>
-      <c r="B122" s="17" t="s">
-        <v>148</v>
+      <c r="A122" s="1">
+        <v>117</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="D122" s="8">
-        <v>123</v>
-      </c>
-      <c r="E122" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="I122" s="22"/>
+        <v>124</v>
+      </c>
+      <c r="E122" t="s">
+        <v>1</v>
+      </c>
+      <c r="I122" s="21"/>
     </row>
     <row r="123" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A123" s="1">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
+      </c>
+      <c r="C123" s="13" t="s">
+        <v>137</v>
       </c>
       <c r="D123" s="8">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E123" t="s">
         <v>1</v>
       </c>
-      <c r="I123" s="22"/>
+      <c r="I123" s="21"/>
     </row>
     <row r="124" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A124" s="1">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C124" s="13" t="s">
-        <v>138</v>
+        <v>39</v>
       </c>
       <c r="D124" s="8">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E124" t="s">
         <v>1</v>
       </c>
-      <c r="I124" s="22"/>
+      <c r="I124" s="21"/>
     </row>
     <row r="125" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A125" s="1">
+      <c r="A125" s="2">
+        <v>102</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D125" s="8">
+        <v>127</v>
+      </c>
+      <c r="E125" t="s">
+        <v>1</v>
+      </c>
+      <c r="I125" s="21"/>
+    </row>
+    <row r="126" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A126" s="3">
+        <v>42</v>
+      </c>
+      <c r="B126" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D126" s="8">
         <v>128</v>
       </c>
-      <c r="B125" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D125" s="8">
-        <v>126</v>
-      </c>
-      <c r="E125" t="s">
-        <v>1</v>
-      </c>
-      <c r="I125" s="22"/>
-    </row>
-    <row r="126" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A126" s="2">
-        <v>102</v>
-      </c>
-      <c r="B126" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D126" s="8">
-        <v>127</v>
-      </c>
       <c r="E126" t="s">
         <v>1</v>
       </c>
-      <c r="I126" s="22"/>
+      <c r="I126" s="21"/>
     </row>
     <row r="127" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A127" s="3">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D127" s="8">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E127" t="s">
         <v>1</v>
       </c>
-      <c r="I127" s="22"/>
+      <c r="I127" s="21"/>
     </row>
     <row r="128" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A128" s="3">
-        <v>52</v>
+        <v>86</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>98</v>
+        <v>122</v>
+      </c>
+      <c r="C128" t="s">
+        <v>66</v>
       </c>
       <c r="D128" s="8">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E128" t="s">
         <v>1</v>
       </c>
-      <c r="I128" s="22"/>
+      <c r="I128" s="21"/>
     </row>
     <row r="129" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A129" s="3">
-        <v>86</v>
-      </c>
-      <c r="B129" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="C129" t="s">
-        <v>67</v>
+      <c r="A129" s="2">
+        <v>135</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>61</v>
       </c>
       <c r="D129" s="8">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E129" t="s">
         <v>1</v>
       </c>
-      <c r="I129" s="22"/>
+      <c r="I129" s="21"/>
     </row>
     <row r="130" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A130" s="2">
-        <v>135</v>
-      </c>
-      <c r="B130" s="2" t="s">
-        <v>62</v>
+      <c r="A130" s="3">
+        <v>6</v>
+      </c>
+      <c r="B130" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C130" s="13" t="s">
+        <v>66</v>
       </c>
       <c r="D130" s="8">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E130" t="s">
         <v>1</v>
       </c>
-      <c r="I130" s="22"/>
+      <c r="I130" s="21"/>
     </row>
     <row r="131" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A131" s="3">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="B131" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="C131" s="13" t="s">
-        <v>67</v>
-      </c>
       <c r="D131" s="8">
+        <v>133</v>
+      </c>
+      <c r="E131" t="s">
+        <v>1</v>
+      </c>
+      <c r="I131" s="21"/>
+    </row>
+    <row r="132" spans="1:9" s="4" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A132" s="6"/>
+      <c r="B132" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="E131" t="s">
-        <v>1</v>
-      </c>
-      <c r="I131" s="22"/>
-    </row>
-    <row r="132" spans="1:9" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A132" s="3">
-        <v>43</v>
-      </c>
-      <c r="B132" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="D132" s="8">
-        <v>133</v>
-      </c>
-      <c r="E132" t="s">
-        <v>1</v>
-      </c>
+      <c r="C132" s="6"/>
+      <c r="D132" s="9">
+        <v>134</v>
+      </c>
+      <c r="E132" s="6"/>
+      <c r="F132" s="6"/>
+      <c r="G132" s="6"/>
+      <c r="H132" s="6"/>
       <c r="I132" s="22"/>
     </row>
-    <row r="133" spans="1:9" s="4" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A133" s="6"/>
-      <c r="B133" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="C133" s="6"/>
-      <c r="D133" s="9">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A134" s="1"/>
+      <c r="B134" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="E133" s="6"/>
-      <c r="F133" s="6"/>
-      <c r="G133" s="6"/>
-      <c r="H133" s="6"/>
-      <c r="I133" s="23"/>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A135" s="1"/>
+      <c r="A135" s="2"/>
       <c r="B135" s="10" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A136" s="2"/>
+      <c r="A136" s="3"/>
       <c r="B136" s="10" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A137" s="3"/>
-      <c r="B137" s="10" t="s">
-        <v>137</v>
-      </c>
-    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E130">
-    <sortCondition ref="D1:D130"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E129">
+    <sortCondition ref="D1:D129"/>
   </sortState>
   <mergeCells count="4">
-    <mergeCell ref="I2:I45"/>
-    <mergeCell ref="I46:I87"/>
-    <mergeCell ref="I110:I133"/>
-    <mergeCell ref="I88:I109"/>
+    <mergeCell ref="I45:I86"/>
+    <mergeCell ref="I109:I132"/>
+    <mergeCell ref="I87:I108"/>
+    <mergeCell ref="I2:I44"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
